--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Bolevec/Databaze Bolevec 2026.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Bolevec/Databaze Bolevec 2026.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3897" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4107" uniqueCount="374">
   <si>
     <t>Datum</t>
   </si>
@@ -366,6 +366,57 @@
     <t>8 min 44 s</t>
   </si>
   <si>
+    <t>12.05.2026</t>
+  </si>
+  <si>
+    <t>9 min 03 s</t>
+  </si>
+  <si>
+    <t>13.05.2026</t>
+  </si>
+  <si>
+    <t>13 min 01 s</t>
+  </si>
+  <si>
+    <t>14.05.2026</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>10 min 31 s</t>
+  </si>
+  <si>
+    <t>15.05.2026</t>
+  </si>
+  <si>
+    <t>8 min 52 s</t>
+  </si>
+  <si>
+    <t>16.05.2026</t>
+  </si>
+  <si>
+    <t>8 min 13 s</t>
+  </si>
+  <si>
+    <t>17.05.2026</t>
+  </si>
+  <si>
+    <t>18.05.2026</t>
+  </si>
+  <si>
+    <t>10 min 14 s</t>
+  </si>
+  <si>
+    <t>19.05.2026</t>
+  </si>
+  <si>
+    <t>9 min 44 s</t>
+  </si>
+  <si>
     <t>01.04.2026</t>
   </si>
   <si>
@@ -450,9 +501,6 @@
     <t>15:30</t>
   </si>
   <si>
-    <t>13 min 01 s</t>
-  </si>
-  <si>
     <t>11.04.2026</t>
   </si>
   <si>
@@ -480,9 +528,6 @@
     <t>14.04.2026</t>
   </si>
   <si>
-    <t>01:30</t>
-  </si>
-  <si>
     <t>12:30</t>
   </si>
   <si>
@@ -540,9 +585,6 @@
     <t>23.04.2026</t>
   </si>
   <si>
-    <t>09:30</t>
-  </si>
-  <si>
     <t>12 min 07 s</t>
   </si>
   <si>
@@ -627,9 +669,6 @@
     <t>05.03.2026</t>
   </si>
   <si>
-    <t>10 min 31 s</t>
-  </si>
-  <si>
     <t>06.03.2026</t>
   </si>
   <si>
@@ -748,9 +787,6 @@
   </si>
   <si>
     <t>25.03.2026</t>
-  </si>
-  <si>
-    <t>10 min 14 s</t>
   </si>
   <si>
     <t>26.03.2026</t>
@@ -3508,6 +3544,1434 @@
         <v>0.0</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="M53" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="N53" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O53" s="3">
+        <v>270.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="P54" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R54" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="S54" s="3">
+        <v>2993.52</v>
+      </c>
+      <c r="T54" s="3">
+        <v>992.0</v>
+      </c>
+      <c r="U54" s="3">
+        <v>2057.0</v>
+      </c>
+      <c r="V54" s="3">
+        <v>1959.0</v>
+      </c>
+      <c r="W54" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X54" s="3">
+        <v>2003.0</v>
+      </c>
+      <c r="Y54" s="3">
+        <v>4527.0</v>
+      </c>
+      <c r="AA54" s="3">
+        <v>3204.0</v>
+      </c>
+      <c r="AB54" s="3">
+        <v>16002.720000000001</v>
+      </c>
+      <c r="AC54" s="3">
+        <v>-0.2000000000007276</v>
+      </c>
+      <c r="AD54" s="3">
+        <v>0.6849688359430508</v>
+      </c>
+      <c r="AI54" s="3">
+        <v>270.0</v>
+      </c>
+      <c r="AJ54" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AK54" s="3">
+        <v>259.0</v>
+      </c>
+      <c r="AL54" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM54" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AN54" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO54" s="3">
+        <v>52.0</v>
+      </c>
+      <c r="AP54" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AQ54" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="AR54" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS54" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT54" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU54" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV54" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M56" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="N56" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O56" s="3">
+        <v>495.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M57" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N57" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O57" s="3">
+        <v>45.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="S58" s="3">
+        <v>4914.05</v>
+      </c>
+      <c r="T58" s="3">
+        <v>244.0</v>
+      </c>
+      <c r="U58" s="3">
+        <v>3950.75</v>
+      </c>
+      <c r="V58" s="3">
+        <v>828.0</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X58" s="3">
+        <v>899.25</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>3784.0</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>3593.0</v>
+      </c>
+      <c r="AB58" s="3">
+        <v>17853.850000000002</v>
+      </c>
+      <c r="AC58" s="3">
+        <v>-0.05000000000291038</v>
+      </c>
+      <c r="AD58" s="3">
+        <v>0.34159864064739986</v>
+      </c>
+      <c r="AI58" s="3">
+        <v>540.0</v>
+      </c>
+      <c r="AJ58" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AK58" s="3">
+        <v>586.0</v>
+      </c>
+      <c r="AL58" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM58" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AN58" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AO58" s="3">
+        <v>55.0</v>
+      </c>
+      <c r="AP58" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="AQ58" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="AR58" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS58" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT58" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU58" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV58" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="M61" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N61" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O61" s="3">
+        <v>360.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="N62" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q63" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R63" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="S63" s="3">
+        <v>4708.57</v>
+      </c>
+      <c r="T63" s="3">
+        <v>992.0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>3006.0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>414.0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>1465.25</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>3053.0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>2712.0</v>
+      </c>
+      <c r="AB63" s="3">
+        <v>15245.219999999998</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0.3500000000021828</v>
+      </c>
+      <c r="AD63" s="3">
+        <v>0.6300933991324876</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>360.0</v>
+      </c>
+      <c r="AJ63" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL63" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM63" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AN63" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>46.0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AR63" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS63" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT63" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU63" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV63" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M66" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N66" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O66" s="3">
+        <v>45.0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M67" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N67" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O67" s="3">
+        <v>90.0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M68" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N68" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O68" s="3">
+        <v>135.0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q69" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R69" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="S69" s="3">
+        <v>4796.27</v>
+      </c>
+      <c r="T69" s="3">
+        <v>3225.0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>4179.25</v>
+      </c>
+      <c r="V69" s="3">
+        <v>1406.0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>1644.75</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>4640.0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>2536.0</v>
+      </c>
+      <c r="AB69" s="3">
+        <v>21288.17</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0.3500000000021828</v>
+      </c>
+      <c r="AD69" s="3">
+        <v>0.5117536589722171</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>236.0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>270.0</v>
+      </c>
+      <c r="AJ69" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>518.0</v>
+      </c>
+      <c r="AL69" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM69" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AN69" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="AO69" s="3">
+        <v>56.0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AR69" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS69" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT69" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU69" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV69" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="M72" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N72" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O72" s="3">
+        <v>90.0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M73" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N73" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O73" s="3">
+        <v>360.0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q74" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R74" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="S74" s="3">
+        <v>4808.139999999999</v>
+      </c>
+      <c r="T74" s="3">
+        <v>2274.0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>5100.0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>2433.0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>629.0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>4233.0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>2793.0</v>
+      </c>
+      <c r="AB74" s="3">
+        <v>22091.54</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>-0.4000000000014552</v>
+      </c>
+      <c r="AD74" s="3">
+        <v>0.5627408723123232</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>450.0</v>
+      </c>
+      <c r="AJ74" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL74" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM74" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="AN74" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>61.0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AR74" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS74" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT74" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU74" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV74" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M77" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N77" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O77" s="3">
+        <v>135.0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P78" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q78" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R78" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S78" s="3">
+        <v>5605.11</v>
+      </c>
+      <c r="T78" s="3">
+        <v>992.0</v>
+      </c>
+      <c r="U78" s="3">
+        <v>4392.75</v>
+      </c>
+      <c r="V78" s="3">
+        <v>1760.0</v>
+      </c>
+      <c r="W78" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X78" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y78" s="3">
+        <v>1095.0</v>
+      </c>
+      <c r="AA78" s="3">
+        <v>477.0</v>
+      </c>
+      <c r="AB78" s="3">
+        <v>14456.659999999996</v>
+      </c>
+      <c r="AC78" s="3">
+        <v>0.20000000000436557</v>
+      </c>
+      <c r="AD78" s="3">
+        <v>0.4407313785011602</v>
+      </c>
+      <c r="AI78" s="3">
+        <v>135.0</v>
+      </c>
+      <c r="AJ78" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK78" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL78" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM78" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN78" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO78" s="3">
+        <v>43.0</v>
+      </c>
+      <c r="AP78" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="AQ78" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="AR78" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS78" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT78" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU78" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV78" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M81" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N81" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O81" s="3">
+        <v>45.0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M82" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N82" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O82" s="3">
+        <v>135.0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="S83" s="3">
+        <v>4229.63</v>
+      </c>
+      <c r="T83" s="3">
+        <v>488.0</v>
+      </c>
+      <c r="U83" s="3">
+        <v>3948.5</v>
+      </c>
+      <c r="V83" s="3">
+        <v>572.0</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X83" s="3">
+        <v>403.0</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>2582.0</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>2455.0</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>14666.929999999998</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>0.20000000000254659</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>0.5656773496786704</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>212.0</v>
+      </c>
+      <c r="AI83" s="3">
+        <v>180.0</v>
+      </c>
+      <c r="AJ83" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK83" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL83" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM83" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="AN83" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AO83" s="3">
+        <v>51.0</v>
+      </c>
+      <c r="AP83" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="AQ83" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AR83" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS83" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT83" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU83" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV83" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M86" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="N86" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O86" s="3">
+        <v>405.0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q87" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R87" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S87" s="3">
+        <v>3391.5099999999998</v>
+      </c>
+      <c r="T87" s="3">
+        <v>787.0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>4633.5</v>
+      </c>
+      <c r="V87" s="3">
+        <v>1898.0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>244.0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>3011.0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>535.0</v>
+      </c>
+      <c r="AB87" s="3">
+        <v>14661.210000000001</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>-0.2000000000007276</v>
+      </c>
+      <c r="AD87" s="3">
+        <v>0.5380752946259264</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>405.0</v>
+      </c>
+      <c r="AJ87" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL87" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AM87" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN87" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO87" s="3">
+        <v>48.0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AR87" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AS87" s="3">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AT87" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU87" s="3">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="AV87" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -3668,7 +5132,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>95</v>
@@ -3688,7 +5152,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>95</v>
@@ -3708,13 +5172,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>55</v>
@@ -3728,7 +5192,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>95</v>
@@ -3740,10 +5204,10 @@
         <v>55</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="M5" s="3">
         <v>5.0</v>
@@ -3757,7 +5221,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>95</v>
@@ -3817,7 +5281,7 @@
         <v>0.0</v>
       </c>
       <c r="AM6" s="1" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="AN6" s="3">
         <v>1.0</v>
@@ -3849,7 +5313,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>99</v>
@@ -3869,13 +5333,13 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>53</v>
@@ -3889,7 +5353,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>99</v>
@@ -3918,7 +5382,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>99</v>
@@ -3947,7 +5411,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>99</v>
@@ -4007,7 +5471,7 @@
         <v>0.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="AN11" s="3">
         <v>2.0</v>
@@ -4039,7 +5503,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>49</v>
@@ -4051,7 +5515,7 @@
         <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>67</v>
@@ -4059,13 +5523,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>55</v>
@@ -4079,7 +5543,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>49</v>
@@ -4099,7 +5563,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>49</v>
@@ -4128,7 +5592,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>49</v>
@@ -4157,7 +5621,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>49</v>
@@ -4220,7 +5684,7 @@
         <v>0.0</v>
       </c>
       <c r="AM17" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="AN17" s="3">
         <v>2.0</v>
@@ -4252,7 +5716,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>63</v>
@@ -4272,13 +5736,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>55</v>
@@ -4292,7 +5756,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>63</v>
@@ -4312,7 +5776,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>63</v>
@@ -4332,7 +5796,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>63</v>
@@ -4361,7 +5825,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>63</v>
@@ -4390,7 +5854,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>63</v>
@@ -4450,7 +5914,7 @@
         <v>0.0</v>
       </c>
       <c r="AM24" s="1" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="AN24" s="3">
         <v>2.0</v>
@@ -4482,7 +5946,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>74</v>
@@ -4502,7 +5966,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>74</v>
@@ -4534,7 +5998,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>74</v>
@@ -4594,7 +6058,7 @@
         <v>0.0</v>
       </c>
       <c r="AM27" s="1" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="AN27" s="3">
         <v>1.0</v>
@@ -4626,7 +6090,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>80</v>
@@ -4646,13 +6110,13 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>55</v>
@@ -4666,7 +6130,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>80</v>
@@ -4686,7 +6150,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>80</v>
@@ -4719,7 +6183,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>80</v>
@@ -4732,7 +6196,7 @@
         <v>92</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>81</v>
@@ -4746,7 +6210,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>80</v>
@@ -4762,7 +6226,7 @@
         <v>53</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>107</v>
@@ -4779,7 +6243,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>80</v>
@@ -4843,7 +6307,7 @@
         <v>0.0</v>
       </c>
       <c r="AM34" s="1" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="AN34" s="3">
         <v>2.0</v>
@@ -4875,7 +6339,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>85</v>
@@ -4887,7 +6351,7 @@
         <v>51</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>114</v>
@@ -4895,7 +6359,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>85</v>
@@ -4915,7 +6379,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>85</v>
@@ -4935,7 +6399,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>85</v>
@@ -4958,7 +6422,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>85</v>
@@ -4987,7 +6451,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>85</v>
@@ -5047,7 +6511,7 @@
         <v>0.0</v>
       </c>
       <c r="AM40" s="1" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="AN40" s="3">
         <v>1.0</v>
@@ -5079,7 +6543,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>95</v>
@@ -5099,13 +6563,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>55</v>
@@ -5119,7 +6583,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>95</v>
@@ -5139,7 +6603,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>95</v>
@@ -5148,7 +6612,7 @@
         <v>92</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>81</v>
@@ -5162,7 +6626,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>95</v>
@@ -5219,7 +6683,7 @@
         <v>0.0</v>
       </c>
       <c r="AM45" s="1" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="AN45" s="3">
         <v>0.0</v>
@@ -5251,7 +6715,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>99</v>
@@ -5271,13 +6735,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>55</v>
@@ -5291,7 +6755,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>99</v>
@@ -5320,7 +6784,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>99</v>
@@ -5380,7 +6844,7 @@
         <v>0.0</v>
       </c>
       <c r="AM49" s="1" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="AN49" s="3">
         <v>1.0</v>
@@ -5412,7 +6876,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>49</v>
@@ -5424,7 +6888,7 @@
         <v>51</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>108</v>
@@ -5432,16 +6896,16 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>86</v>
@@ -5452,7 +6916,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>49</v>
@@ -5472,7 +6936,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>49</v>
@@ -5484,7 +6948,7 @@
         <v>55</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>90</v>
@@ -5501,7 +6965,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>49</v>
@@ -5510,7 +6974,7 @@
         <v>58</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>52</v>
@@ -5530,7 +6994,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>49</v>
@@ -5590,7 +7054,7 @@
         <v>4.0</v>
       </c>
       <c r="AM55" s="1" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="AN55" s="3">
         <v>2.0</v>
@@ -5622,7 +7086,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>63</v>
@@ -5642,19 +7106,19 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>108</v>
@@ -5662,7 +7126,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>63</v>
@@ -5674,7 +7138,7 @@
         <v>53</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>65</v>
@@ -5682,7 +7146,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>63</v>
@@ -5705,7 +7169,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>63</v>
@@ -5734,7 +7198,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>63</v>
@@ -5797,7 +7261,7 @@
         <v>3.0</v>
       </c>
       <c r="AM61" s="1" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="AN61" s="3">
         <v>1.0</v>
@@ -5829,7 +7293,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>74</v>
@@ -5849,13 +7313,13 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>55</v>
@@ -5869,7 +7333,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>74</v>
@@ -5889,7 +7353,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>74</v>
@@ -5918,7 +7382,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>74</v>
@@ -5947,7 +7411,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>74</v>
@@ -6007,7 +7471,7 @@
         <v>0.0</v>
       </c>
       <c r="AM67" s="1" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="AN67" s="3">
         <v>2.0</v>
@@ -6039,7 +7503,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>80</v>
@@ -6051,7 +7515,7 @@
         <v>51</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>114</v>
@@ -6059,13 +7523,13 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>87</v>
@@ -6079,7 +7543,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>80</v>
@@ -6099,7 +7563,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>80</v>
@@ -6128,7 +7592,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>80</v>
@@ -6191,7 +7655,7 @@
         <v>0.0</v>
       </c>
       <c r="AM72" s="1" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="AN72" s="3">
         <v>1.0</v>
@@ -6223,7 +7687,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>85</v>
@@ -6243,13 +7707,13 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>55</v>
@@ -6263,7 +7727,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>85</v>
@@ -6283,7 +7747,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>85</v>
@@ -6298,10 +7762,10 @@
         <v>81</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="M76" s="3">
         <v>2.0</v>
@@ -6315,7 +7779,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>85</v>
@@ -6375,7 +7839,7 @@
         <v>0.0</v>
       </c>
       <c r="AM77" s="1" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="AN77" s="3">
         <v>1.0</v>
@@ -6407,7 +7871,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>95</v>
@@ -6427,7 +7891,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>95</v>
@@ -6447,7 +7911,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>95</v>
@@ -6470,7 +7934,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>95</v>
@@ -6499,7 +7963,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>95</v>
@@ -6559,7 +8023,7 @@
         <v>0.0</v>
       </c>
       <c r="AM82" s="1" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="AN82" s="3">
         <v>1.0</v>
@@ -6591,7 +8055,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>99</v>
@@ -6611,7 +8075,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>99</v>
@@ -6631,7 +8095,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>99</v>
@@ -6643,7 +8107,7 @@
         <v>59</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>67</v>
@@ -6660,7 +8124,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>99</v>
@@ -6723,7 +8187,7 @@
         <v>0.0</v>
       </c>
       <c r="AM86" s="1" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="AN86" s="3">
         <v>1.0</v>
@@ -6755,7 +8219,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>49</v>
@@ -6767,7 +8231,7 @@
         <v>51</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>67</v>
@@ -6775,7 +8239,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>49</v>
@@ -6795,7 +8259,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>49</v>
@@ -6824,7 +8288,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>49</v>
@@ -6853,7 +8317,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>49</v>
@@ -6913,7 +8377,7 @@
         <v>0.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="AN91" s="3">
         <v>2.0</v>
@@ -6945,7 +8409,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>63</v>
@@ -6965,7 +8429,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>63</v>
@@ -6994,7 +8458,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>63</v>
@@ -7023,7 +8487,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>63</v>
@@ -7077,7 +8541,7 @@
         <v>0.0</v>
       </c>
       <c r="AM95" s="1" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="AN95" s="3">
         <v>2.0</v>
@@ -7109,7 +8573,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>74</v>
@@ -7129,7 +8593,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>74</v>
@@ -7158,7 +8622,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>74</v>
@@ -7212,7 +8676,7 @@
         <v>1.0</v>
       </c>
       <c r="AM98" s="1" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="AN98" s="3">
         <v>1.0</v>
@@ -7244,7 +8708,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>80</v>
@@ -7264,7 +8728,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>80</v>
@@ -7284,7 +8748,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>80</v>
@@ -7313,7 +8777,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>80</v>
@@ -7367,7 +8831,7 @@
         <v>1.0</v>
       </c>
       <c r="AM102" s="1" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="AN102" s="3">
         <v>1.0</v>
@@ -7399,7 +8863,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>85</v>
@@ -7419,7 +8883,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>85</v>
@@ -7439,7 +8903,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>85</v>
@@ -7468,7 +8932,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>85</v>
@@ -7480,7 +8944,7 @@
         <v>59</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="L106" s="2" t="s">
         <v>67</v>
@@ -7497,7 +8961,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>85</v>
@@ -7557,7 +9021,7 @@
         <v>0.0</v>
       </c>
       <c r="AM107" s="1" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="AN107" s="3">
         <v>2.0</v>
@@ -7589,7 +9053,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>95</v>
@@ -7609,7 +9073,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>95</v>
@@ -7629,7 +9093,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>95</v>
@@ -7661,7 +9125,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>95</v>
@@ -7724,7 +9188,7 @@
         <v>0.0</v>
       </c>
       <c r="AM111" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="AN111" s="3">
         <v>1.0</v>
@@ -7756,7 +9220,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>99</v>
@@ -7765,7 +9229,7 @@
         <v>50</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>59</v>
@@ -7776,7 +9240,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>99</v>
@@ -7796,7 +9260,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>99</v>
@@ -7825,7 +9289,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>99</v>
@@ -7888,7 +9352,7 @@
         <v>2.0</v>
       </c>
       <c r="AM115" s="1" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="AN115" s="3">
         <v>1.0</v>
@@ -7920,7 +9384,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>49</v>
@@ -7940,7 +9404,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>49</v>
@@ -7963,7 +9427,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>49</v>
@@ -7983,7 +9447,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>49</v>
@@ -8012,7 +9476,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>49</v>
@@ -8041,7 +9505,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>49</v>
@@ -8101,7 +9565,7 @@
         <v>2.0</v>
       </c>
       <c r="AM121" s="1" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="AN121" s="3">
         <v>2.0</v>
@@ -8133,7 +9597,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>63</v>
@@ -8145,7 +9609,7 @@
         <v>51</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>108</v>
@@ -8153,7 +9617,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>63</v>
@@ -8173,7 +9637,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>63</v>
@@ -8202,7 +9666,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>63</v>
@@ -8231,7 +9695,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>63</v>
@@ -8294,7 +9758,7 @@
         <v>1.0</v>
       </c>
       <c r="AM126" s="1" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="AN126" s="3">
         <v>2.0</v>
@@ -8326,7 +9790,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>74</v>
@@ -8346,7 +9810,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>74</v>
@@ -8366,7 +9830,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>74</v>
@@ -8395,7 +9859,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>74</v>
@@ -8424,7 +9888,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>74</v>
@@ -8484,7 +9948,7 @@
         <v>0.0</v>
       </c>
       <c r="AM131" s="1" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="AN131" s="3">
         <v>2.0</v>
@@ -8516,7 +9980,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>80</v>
@@ -8536,7 +10000,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>80</v>
@@ -8556,7 +10020,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>80</v>
@@ -8588,7 +10052,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>80</v>
@@ -8648,7 +10112,7 @@
         <v>0.0</v>
       </c>
       <c r="AM135" s="1" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="AN135" s="3">
         <v>1.0</v>
@@ -8680,7 +10144,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>85</v>
@@ -8692,7 +10156,7 @@
         <v>51</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>55</v>
@@ -8700,7 +10164,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>85</v>
@@ -8720,7 +10184,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>85</v>
@@ -8743,7 +10207,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>85</v>
@@ -8752,7 +10216,7 @@
         <v>91</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>81</v>
@@ -8772,7 +10236,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>85</v>
@@ -8832,7 +10296,7 @@
         <v>1.0</v>
       </c>
       <c r="AM140" s="1" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="AN140" s="3">
         <v>1.0</v>
@@ -8864,7 +10328,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>95</v>
@@ -8884,7 +10348,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>95</v>
@@ -8893,13 +10357,13 @@
         <v>68</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>81</v>
       </c>
       <c r="L142" s="2" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="M142" s="3">
         <v>9.0</v>
@@ -8913,7 +10377,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>95</v>
@@ -8967,7 +10431,7 @@
         <v>3.0</v>
       </c>
       <c r="AM143" s="1" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="AN143" s="3">
         <v>1.0</v>
@@ -8999,7 +10463,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>99</v>
@@ -9019,7 +10483,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>99</v>
@@ -9051,7 +10515,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>99</v>
@@ -9080,7 +10544,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>99</v>
@@ -9134,7 +10598,7 @@
         <v>0.0</v>
       </c>
       <c r="AM147" s="1" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="AN147" s="3">
         <v>2.0</v>
@@ -9324,7 +10788,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>74</v>
@@ -9344,7 +10808,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>74</v>
@@ -9356,7 +10820,7 @@
         <v>82</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>107</v>
@@ -9364,7 +10828,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>74</v>
@@ -9384,7 +10848,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>74</v>
@@ -9413,7 +10877,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>74</v>
@@ -9473,7 +10937,7 @@
         <v>0.0</v>
       </c>
       <c r="AM6" s="1" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="AN6" s="3">
         <v>1.0</v>
@@ -9505,7 +10969,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>80</v>
@@ -9514,24 +10978,24 @@
         <v>66</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>81</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>55</v>
@@ -9545,7 +11009,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>80</v>
@@ -9565,13 +11029,13 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>53</v>
@@ -9585,7 +11049,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>80</v>
@@ -9597,7 +11061,7 @@
         <v>55</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>90</v>
@@ -9614,22 +11078,22 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>81</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="M12" s="3">
         <v>3.0</v>
@@ -9643,7 +11107,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>80</v>
@@ -9703,7 +11167,7 @@
         <v>1.0</v>
       </c>
       <c r="AM13" s="1" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="AN13" s="3">
         <v>2.0</v>
@@ -9735,7 +11199,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>85</v>
@@ -9744,24 +11208,24 @@
         <v>66</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>81</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -9775,7 +11239,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>85</v>
@@ -9790,7 +11254,7 @@
         <v>88</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>67</v>
@@ -9798,7 +11262,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>85</v>
@@ -9827,7 +11291,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>85</v>
@@ -9856,7 +11320,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>85</v>
@@ -9916,7 +11380,7 @@
         <v>0.0</v>
       </c>
       <c r="AM19" s="1" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="AN19" s="3">
         <v>2.0</v>
@@ -9948,7 +11412,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>95</v>
@@ -9960,7 +11424,7 @@
         <v>51</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>55</v>
@@ -9968,7 +11432,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>95</v>
@@ -9988,13 +11452,13 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>53</v>
@@ -10008,13 +11472,13 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>55</v>
@@ -10037,7 +11501,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>95</v>
@@ -10066,7 +11530,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>95</v>
@@ -10126,7 +11590,7 @@
         <v>0.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="AN25" s="3">
         <v>2.0</v>
@@ -10158,7 +11622,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>99</v>
@@ -10178,7 +11642,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>99</v>
@@ -10198,13 +11662,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>55</v>
@@ -10227,7 +11691,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>99</v>
@@ -10287,7 +11751,7 @@
         <v>1.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>203</v>
+        <v>123</v>
       </c>
       <c r="AN29" s="3">
         <v>1.0</v>
@@ -10319,7 +11783,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>49</v>
@@ -10328,10 +11792,10 @@
         <v>66</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>51</v>
@@ -10339,7 +11803,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>49</v>
@@ -10359,13 +11823,13 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>96</v>
@@ -10374,24 +11838,24 @@
         <v>53</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>70</v>
@@ -10399,19 +11863,19 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>55</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>90</v>
@@ -10422,13 +11886,13 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>53</v>
@@ -10451,7 +11915,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>49</v>
@@ -10511,7 +11975,7 @@
         <v>0.0</v>
       </c>
       <c r="AM36" s="1" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="AN36" s="3">
         <v>1.0</v>
@@ -10543,7 +12007,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>63</v>
@@ -10563,7 +12027,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>63</v>
@@ -10583,7 +12047,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>63</v>
@@ -10612,7 +12076,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>63</v>
@@ -10641,7 +12105,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>63</v>
@@ -10701,7 +12165,7 @@
         <v>1.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="AN41" s="3">
         <v>2.0</v>
@@ -10733,7 +12197,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>74</v>
@@ -10753,7 +12217,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>74</v>
@@ -10765,7 +12229,7 @@
         <v>87</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>87</v>
@@ -10773,7 +12237,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>74</v>
@@ -10802,19 +12266,19 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>74</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>100</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>70</v>
@@ -10825,7 +12289,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>74</v>
@@ -10885,7 +12349,7 @@
         <v>0.0</v>
       </c>
       <c r="AM46" s="1" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="AN46" s="3">
         <v>1.0</v>
@@ -10917,7 +12381,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>80</v>
@@ -10937,13 +12401,13 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>55</v>
@@ -10960,13 +12424,13 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>59</v>
@@ -10989,7 +12453,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>80</v>
@@ -11043,7 +12507,7 @@
         <v>0.0</v>
       </c>
       <c r="AM50" s="1" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="AN50" s="3">
         <v>1.0</v>
@@ -11075,7 +12539,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>85</v>
@@ -11095,27 +12559,27 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>56</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>85</v>
@@ -11135,13 +12599,13 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>55</v>
@@ -11158,13 +12622,13 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>53</v>
@@ -11187,7 +12651,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>85</v>
@@ -11250,7 +12714,7 @@
         <v>1.0</v>
       </c>
       <c r="AM56" s="1" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="AN56" s="3">
         <v>1.0</v>
@@ -11282,7 +12746,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>95</v>
@@ -11302,7 +12766,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>95</v>
@@ -11322,13 +12786,13 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>56</v>
@@ -11342,13 +12806,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>55</v>
@@ -11365,7 +12829,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>95</v>
@@ -11394,7 +12858,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>95</v>
@@ -11454,7 +12918,7 @@
         <v>0.0</v>
       </c>
       <c r="AM62" s="1" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="AN62" s="3">
         <v>1.0</v>
@@ -11486,7 +12950,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>99</v>
@@ -11498,7 +12962,7 @@
         <v>51</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>108</v>
@@ -11506,7 +12970,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>99</v>
@@ -11526,19 +12990,19 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>70</v>
@@ -11546,13 +13010,13 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>55</v>
@@ -11575,7 +13039,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>99</v>
@@ -11635,7 +13099,7 @@
         <v>0.0</v>
       </c>
       <c r="AM67" s="1" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="AN67" s="3">
         <v>1.0</v>
@@ -11667,7 +13131,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>49</v>
@@ -11679,7 +13143,7 @@
         <v>51</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>108</v>
@@ -11687,7 +13151,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>49</v>
@@ -11699,7 +13163,7 @@
         <v>53</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>65</v>
@@ -11707,13 +13171,13 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>53</v>
@@ -11722,24 +13186,24 @@
         <v>64</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>55</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>114</v>
@@ -11756,7 +13220,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>49</v>
@@ -11785,7 +13249,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>49</v>
@@ -11845,7 +13309,7 @@
         <v>0.0</v>
       </c>
       <c r="AM73" s="1" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="AN73" s="3">
         <v>2.0</v>
@@ -11877,7 +13341,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>63</v>
@@ -11897,13 +13361,13 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>55</v>
@@ -11917,7 +13381,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>63</v>
@@ -11929,15 +13393,15 @@
         <v>59</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>63</v>
@@ -11960,7 +13424,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>63</v>
@@ -11989,7 +13453,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>63</v>
@@ -12018,7 +13482,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>63</v>
@@ -12078,7 +13542,7 @@
         <v>0.0</v>
       </c>
       <c r="AM80" s="1" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="AN80" s="3">
         <v>2.0</v>
@@ -12110,7 +13574,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>74</v>
@@ -12130,7 +13594,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>74</v>
@@ -12159,7 +13623,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>74</v>
@@ -12188,7 +13652,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>74</v>
@@ -12245,7 +13709,7 @@
         <v>0.0</v>
       </c>
       <c r="AM84" s="1" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="AN84" s="3">
         <v>2.0</v>
@@ -12277,7 +13741,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>80</v>
@@ -12289,7 +13753,7 @@
         <v>51</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>114</v>
@@ -12297,13 +13761,13 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>55</v>
@@ -12317,7 +13781,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>80</v>
@@ -12337,19 +13801,19 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>70</v>
@@ -12357,13 +13821,13 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>55</v>
@@ -12380,19 +13844,19 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>114</v>
@@ -12403,7 +13867,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>80</v>
@@ -12463,7 +13927,7 @@
         <v>0.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="AN91" s="3">
         <v>0.0</v>
@@ -12495,7 +13959,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>85</v>
@@ -12515,13 +13979,13 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>55</v>
@@ -12535,7 +13999,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>85</v>
@@ -12547,7 +14011,7 @@
         <v>53</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>108</v>
@@ -12555,19 +14019,19 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>114</v>
@@ -12575,7 +14039,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>85</v>
@@ -12604,13 +14068,13 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>53</v>
@@ -12633,7 +14097,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>85</v>
@@ -12693,7 +14157,7 @@
         <v>0.0</v>
       </c>
       <c r="AM98" s="1" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="AN98" s="3">
         <v>2.0</v>
@@ -12725,7 +14189,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>95</v>
@@ -12745,7 +14209,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>95</v>
@@ -12765,19 +14229,19 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>70</v>
@@ -12785,7 +14249,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>95</v>
@@ -12797,7 +14261,7 @@
         <v>53</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>108</v>
@@ -12805,13 +14269,13 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>55</v>
@@ -12834,7 +14298,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>95</v>
@@ -12863,7 +14327,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>95</v>
@@ -12920,7 +14384,7 @@
         <v>1.0</v>
       </c>
       <c r="AM105" s="1" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="AN105" s="3">
         <v>2.0</v>
@@ -12952,7 +14416,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>99</v>
@@ -12972,13 +14436,13 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>55</v>
@@ -12992,13 +14456,13 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>55</v>
@@ -13021,7 +14485,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>99</v>
@@ -13078,7 +14542,7 @@
         <v>0.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="AN109" s="3">
         <v>1.0</v>
@@ -13110,7 +14574,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>49</v>
@@ -13130,13 +14594,13 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>55</v>
@@ -13150,7 +14614,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>49</v>
@@ -13170,13 +14634,13 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I113" s="2" t="s">
         <v>55</v>
@@ -13199,7 +14663,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>49</v>
@@ -13228,7 +14692,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>49</v>
@@ -13285,7 +14749,7 @@
         <v>0.0</v>
       </c>
       <c r="AM115" s="1" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="AN115" s="3">
         <v>2.0</v>
@@ -13317,7 +14781,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>63</v>
@@ -13337,7 +14801,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>63</v>
@@ -13357,19 +14821,19 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>70</v>
@@ -13377,7 +14841,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>63</v>
@@ -13406,7 +14870,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>63</v>
@@ -13435,7 +14899,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>63</v>
@@ -13495,7 +14959,7 @@
         <v>0.0</v>
       </c>
       <c r="AM121" s="1" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="AN121" s="3">
         <v>2.0</v>
@@ -13527,7 +14991,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>74</v>
@@ -13547,7 +15011,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>74</v>
@@ -13570,13 +15034,13 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>74</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I124" s="2" t="s">
         <v>53</v>
@@ -13599,7 +15063,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>74</v>
@@ -13659,7 +15123,7 @@
         <v>0.0</v>
       </c>
       <c r="AM125" s="1" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="AN125" s="3">
         <v>1.0</v>
@@ -13691,7 +15155,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>80</v>
@@ -13711,13 +15175,13 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>55</v>
@@ -13731,7 +15195,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>80</v>
@@ -13751,13 +15215,13 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I129" s="2" t="s">
         <v>55</v>
@@ -13780,7 +15244,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>80</v>
@@ -13792,13 +15256,13 @@
         <v>53</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="K130" s="2" t="s">
         <v>70</v>
       </c>
       <c r="L130" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="M130" s="3">
         <v>2.0</v>
@@ -13812,7 +15276,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>80</v>
@@ -13872,7 +15336,7 @@
         <v>0.0</v>
       </c>
       <c r="AM131" s="1" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="AN131" s="3">
         <v>2.0</v>
@@ -13904,7 +15368,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>85</v>
@@ -13916,7 +15380,7 @@
         <v>51</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>114</v>
@@ -13924,7 +15388,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>85</v>
@@ -13944,33 +15408,33 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I135" s="2" t="s">
         <v>55</v>
@@ -13993,7 +15457,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>85</v>
@@ -14005,7 +15469,7 @@
         <v>59</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="L136" s="2" t="s">
         <v>67</v>
@@ -14016,7 +15480,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>85</v>
@@ -14076,7 +15540,7 @@
         <v>0.0</v>
       </c>
       <c r="AM137" s="1" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="AN137" s="3">
         <v>1.0</v>
@@ -14108,7 +15572,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>95</v>
@@ -14128,13 +15592,13 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>55</v>
@@ -14148,7 +15612,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>95</v>
@@ -14168,13 +15632,13 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I141" s="2" t="s">
         <v>55</v>
@@ -14197,7 +15661,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>95</v>
@@ -14226,7 +15690,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>95</v>
@@ -14286,7 +15750,7 @@
         <v>0.0</v>
       </c>
       <c r="AM143" s="1" t="s">
-        <v>244</v>
+        <v>130</v>
       </c>
       <c r="AN143" s="3">
         <v>2.0</v>
@@ -14318,7 +15782,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>99</v>
@@ -14338,13 +15802,13 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>55</v>
@@ -14358,7 +15822,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>99</v>
@@ -14378,7 +15842,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>99</v>
@@ -14401,13 +15865,13 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I148" s="2" t="s">
         <v>53</v>
@@ -14430,7 +15894,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>99</v>
@@ -14490,7 +15954,7 @@
         <v>0.0</v>
       </c>
       <c r="AM149" s="1" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="AN149" s="3">
         <v>1.0</v>
@@ -14522,7 +15986,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>49</v>
@@ -14545,7 +16009,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>49</v>
@@ -14565,13 +16029,13 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>55</v>
@@ -14585,7 +16049,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>49</v>
@@ -14614,7 +16078,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>49</v>
@@ -14637,7 +16101,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>49</v>
@@ -14666,7 +16130,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>49</v>
@@ -14726,7 +16190,7 @@
         <v>1.0</v>
       </c>
       <c r="AM156" s="1" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="AN156" s="3">
         <v>2.0</v>
@@ -14758,7 +16222,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>63</v>
@@ -14770,7 +16234,7 @@
         <v>51</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>67</v>
@@ -14778,7 +16242,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>63</v>
@@ -14798,7 +16262,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>63</v>
@@ -14827,7 +16291,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>63</v>
@@ -14856,7 +16320,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>63</v>
@@ -14916,7 +16380,7 @@
         <v>0.0</v>
       </c>
       <c r="AM161" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="AN161" s="3">
         <v>2.0</v>
@@ -14948,7 +16412,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>74</v>
@@ -14968,7 +16432,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>74</v>
@@ -14988,7 +16452,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>74</v>
@@ -15017,7 +16481,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>74</v>
@@ -15046,7 +16510,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>74</v>
@@ -15100,7 +16564,7 @@
         <v>0.0</v>
       </c>
       <c r="AM166" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="AN166" s="3">
         <v>2.0</v>
@@ -15132,7 +16596,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>80</v>
@@ -15152,7 +16616,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>80</v>
@@ -15172,13 +16636,13 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I169" s="2" t="s">
         <v>55</v>
@@ -15195,7 +16659,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>80</v>
@@ -15207,7 +16671,7 @@
         <v>53</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="L170" s="2" t="s">
         <v>114</v>
@@ -15224,7 +16688,7 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>80</v>
@@ -15284,7 +16748,7 @@
         <v>0.0</v>
       </c>
       <c r="AM171" s="1" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="AN171" s="3">
         <v>1.0</v>
@@ -15316,7 +16780,7 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>85</v>
@@ -15328,21 +16792,21 @@
         <v>51</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I173" s="2" t="s">
         <v>55</v>
@@ -15365,7 +16829,7 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>85</v>
@@ -15377,7 +16841,7 @@
         <v>53</v>
       </c>
       <c r="J174" s="2" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="L174" s="2" t="s">
         <v>108</v>
@@ -15394,7 +16858,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>85</v>
@@ -15451,7 +16915,7 @@
         <v>1.0</v>
       </c>
       <c r="AM175" s="1" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="AN175" s="3">
         <v>2.0</v>
@@ -15641,7 +17105,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>74</v>
@@ -15661,7 +17125,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>74</v>
@@ -15681,7 +17145,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>74</v>
@@ -15704,7 +17168,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>74</v>
@@ -15733,7 +17197,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>74</v>
@@ -15787,7 +17251,7 @@
         <v>0.0</v>
       </c>
       <c r="AM6" s="1" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="AN6" s="3">
         <v>1.0</v>
@@ -15819,7 +17283,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>80</v>
@@ -15839,7 +17303,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>80</v>
@@ -15859,13 +17323,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>53</v>
@@ -15882,7 +17346,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>80</v>
@@ -15942,7 +17406,7 @@
         <v>0.0</v>
       </c>
       <c r="AM10" s="1" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AN10" s="3">
         <v>0.0</v>
@@ -15974,7 +17438,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>85</v>
@@ -15994,16 +17458,16 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="M12" s="3">
         <v>1.0</v>
@@ -16017,7 +17481,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>85</v>
@@ -16080,7 +17544,7 @@
         <v>1.0</v>
       </c>
       <c r="AM13" s="1" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="AN13" s="3">
         <v>1.0</v>
@@ -16112,7 +17576,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>95</v>
@@ -16132,22 +17596,22 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>55</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="M15" s="3">
         <v>1.0</v>
@@ -16161,13 +17625,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>53</v>
@@ -16190,7 +17654,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>95</v>
@@ -16244,7 +17708,7 @@
         <v>0.0</v>
       </c>
       <c r="AM17" s="1" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="AN17" s="3">
         <v>2.0</v>
@@ -16276,7 +17740,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>99</v>
@@ -16296,7 +17760,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>99</v>
@@ -16316,7 +17780,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>99</v>
@@ -16328,7 +17792,7 @@
         <v>53</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>70</v>
@@ -16336,13 +17800,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>53</v>
@@ -16365,7 +17829,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>99</v>
@@ -16419,7 +17883,7 @@
         <v>0.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="AN22" s="3">
         <v>1.0</v>
@@ -16451,7 +17915,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>49</v>
@@ -16471,7 +17935,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>49</v>
@@ -16491,7 +17955,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>49</v>
@@ -16511,13 +17975,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>69</v>
@@ -16540,7 +18004,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>49</v>
@@ -16594,7 +18058,7 @@
         <v>0.0</v>
       </c>
       <c r="AM27" s="1" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AN27" s="3">
         <v>1.0</v>
@@ -16626,7 +18090,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>63</v>
@@ -16646,7 +18110,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>63</v>
@@ -16666,7 +18130,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>63</v>
@@ -16695,7 +18159,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>63</v>
@@ -16752,7 +18216,7 @@
         <v>0.0</v>
       </c>
       <c r="AM31" s="1" t="s">
-        <v>203</v>
+        <v>123</v>
       </c>
       <c r="AN31" s="3">
         <v>1.0</v>
@@ -16784,7 +18248,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>74</v>
@@ -16796,7 +18260,7 @@
         <v>51</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>55</v>
@@ -16804,7 +18268,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>74</v>
@@ -16813,7 +18277,7 @@
         <v>50</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>75</v>
@@ -16824,7 +18288,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>74</v>
@@ -16853,7 +18317,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>74</v>
@@ -16876,7 +18340,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>74</v>
@@ -16930,7 +18394,7 @@
         <v>1.0</v>
       </c>
       <c r="AM36" s="1" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="AN36" s="3">
         <v>1.0</v>
@@ -16962,7 +18426,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>80</v>
@@ -16982,7 +18446,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>80</v>
@@ -17002,7 +18466,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>80</v>
@@ -17011,7 +18475,7 @@
         <v>54</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>81</v>
@@ -17025,7 +18489,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>80</v>
@@ -17085,7 +18549,7 @@
         <v>2.0</v>
       </c>
       <c r="AM40" s="1" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="AN40" s="3">
         <v>0.0</v>
@@ -17117,7 +18581,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>85</v>
@@ -17137,7 +18601,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>85</v>
@@ -17157,13 +18621,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>53</v>
@@ -17186,7 +18650,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>85</v>
@@ -17240,7 +18704,7 @@
         <v>0.0</v>
       </c>
       <c r="AM44" s="1" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="AN44" s="3">
         <v>1.0</v>
@@ -17272,7 +18736,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>95</v>
@@ -17292,7 +18756,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>95</v>
@@ -17312,13 +18776,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>55</v>
@@ -17335,13 +18799,13 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>53</v>
@@ -17364,7 +18828,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>95</v>
@@ -17418,7 +18882,7 @@
         <v>1.0</v>
       </c>
       <c r="AM49" s="1" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="AN49" s="3">
         <v>1.0</v>
@@ -17450,7 +18914,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>99</v>
@@ -17470,7 +18934,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>99</v>
@@ -17490,19 +18954,19 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>81</v>
@@ -17510,13 +18974,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>53</v>
@@ -17539,7 +19003,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>99</v>
@@ -17593,7 +19057,7 @@
         <v>1.0</v>
       </c>
       <c r="AM54" s="1" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="AN54" s="3">
         <v>1.0</v>
@@ -17625,7 +19089,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>49</v>
@@ -17645,7 +19109,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>49</v>
@@ -17665,7 +19129,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>49</v>
@@ -17685,39 +19149,39 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>55</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>90</v>
@@ -17728,7 +19192,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>49</v>
@@ -17757,7 +19221,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>49</v>
@@ -17811,7 +19275,7 @@
         <v>0.0</v>
       </c>
       <c r="AM61" s="1" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="AN61" s="3">
         <v>1.0</v>
@@ -17843,7 +19307,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>63</v>
@@ -17863,7 +19327,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>63</v>
@@ -17883,7 +19347,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>63</v>
@@ -17903,7 +19367,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>63</v>
@@ -17932,7 +19396,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>63</v>
@@ -17989,7 +19453,7 @@
         <v>3.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="AN66" s="3">
         <v>1.0</v>
@@ -18021,7 +19485,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>74</v>
@@ -18041,13 +19505,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>55</v>
@@ -18061,7 +19525,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>74</v>
@@ -18081,7 +19545,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>74</v>
@@ -18110,7 +19574,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>74</v>
@@ -18139,7 +19603,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>74</v>
@@ -18199,7 +19663,7 @@
         <v>1.0</v>
       </c>
       <c r="AM72" s="1" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="AN72" s="3">
         <v>2.0</v>
@@ -18231,7 +19695,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>80</v>
@@ -18251,7 +19715,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>80</v>
@@ -18271,13 +19735,13 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>96</v>
@@ -18291,13 +19755,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>53</v>
@@ -18320,7 +19784,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>80</v>
@@ -18374,7 +19838,7 @@
         <v>0.0</v>
       </c>
       <c r="AM77" s="1" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="AN77" s="3">
         <v>1.0</v>
@@ -18406,7 +19870,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>85</v>
@@ -18426,13 +19890,13 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>96</v>
@@ -18446,7 +19910,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>85</v>
@@ -18466,7 +19930,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>85</v>
@@ -18475,7 +19939,7 @@
         <v>54</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>81</v>
@@ -18489,7 +19953,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>85</v>
@@ -18549,7 +20013,7 @@
         <v>1.0</v>
       </c>
       <c r="AM82" s="1" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AN82" s="3">
         <v>0.0</v>
@@ -18581,7 +20045,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>95</v>
@@ -18601,7 +20065,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>95</v>
@@ -18621,27 +20085,27 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>95</v>
@@ -18661,13 +20125,13 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>53</v>
@@ -18690,7 +20154,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>95</v>
@@ -18744,7 +20208,7 @@
         <v>1.0</v>
       </c>
       <c r="AM88" s="1" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="AN88" s="3">
         <v>1.0</v>
@@ -18776,7 +20240,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>99</v>
@@ -18796,7 +20260,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>99</v>
@@ -18850,7 +20314,7 @@
         <v>2.0</v>
       </c>
       <c r="AM90" s="1" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AN90" s="3">
         <v>0.0</v>
@@ -18882,7 +20346,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>49</v>
@@ -18902,13 +20366,13 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>65</v>
@@ -18922,7 +20386,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>49</v>
@@ -18942,7 +20406,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>49</v>
@@ -18971,7 +20435,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>49</v>
@@ -19000,7 +20464,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>49</v>
@@ -19054,7 +20518,7 @@
         <v>1.0</v>
       </c>
       <c r="AM96" s="1" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="AN96" s="3">
         <v>2.0</v>
@@ -19086,7 +20550,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>63</v>
@@ -19106,7 +20570,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>63</v>
@@ -19126,7 +20590,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>63</v>
@@ -19138,7 +20602,7 @@
         <v>55</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>108</v>
@@ -19155,7 +20619,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>63</v>
@@ -19184,7 +20648,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>63</v>
@@ -19244,7 +20708,7 @@
         <v>1.0</v>
       </c>
       <c r="AM101" s="1" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="AN101" s="3">
         <v>2.0</v>
@@ -19276,7 +20740,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>74</v>
@@ -19296,13 +20760,13 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>55</v>
@@ -19316,7 +20780,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>74</v>
@@ -19345,7 +20809,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>74</v>
@@ -19368,7 +20832,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>74</v>
@@ -19422,7 +20886,7 @@
         <v>0.0</v>
       </c>
       <c r="AM106" s="1" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="AN106" s="3">
         <v>1.0</v>
@@ -19454,7 +20918,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>80</v>
@@ -19474,13 +20938,13 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>53</v>
@@ -19503,7 +20967,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>80</v>
@@ -19557,7 +21021,7 @@
         <v>0.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="AN109" s="3">
         <v>1.0</v>
@@ -19589,7 +21053,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>85</v>
@@ -19609,7 +21073,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>85</v>
@@ -19629,7 +21093,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>85</v>
@@ -19649,13 +21113,13 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>55</v>
@@ -19669,13 +21133,13 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I114" s="2" t="s">
         <v>53</v>
@@ -19698,7 +21162,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>85</v>
@@ -19761,7 +21225,7 @@
         <v>1.0</v>
       </c>
       <c r="AM115" s="1" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="AN115" s="3">
         <v>1.0</v>
@@ -19793,13 +21257,13 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>55</v>
@@ -19813,7 +21277,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>95</v>
@@ -19833,7 +21297,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>95</v>
@@ -19853,7 +21317,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>95</v>
@@ -19865,21 +21329,21 @@
         <v>56</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="I120" s="2" t="s">
         <v>55</v>
@@ -19902,13 +21366,13 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>53</v>
@@ -19931,7 +21395,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>95</v>
@@ -19985,7 +21449,7 @@
         <v>0.0</v>
       </c>
       <c r="AM122" s="1" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="AN122" s="3">
         <v>2.0</v>
@@ -20017,7 +21481,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>99</v>
@@ -20037,13 +21501,13 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>55</v>
@@ -20057,7 +21521,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>99</v>
@@ -20077,7 +21541,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>99</v>
@@ -20106,7 +21570,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>99</v>
@@ -20160,7 +21624,7 @@
         <v>1.0</v>
       </c>
       <c r="AM127" s="1" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="AN127" s="3">
         <v>1.0</v>
@@ -20192,7 +21656,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>49</v>
@@ -20212,7 +21676,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>49</v>
@@ -20232,13 +21696,13 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="I130" s="2" t="s">
         <v>55</v>
@@ -20255,7 +21719,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>49</v>
@@ -20315,7 +21779,7 @@
         <v>0.0</v>
       </c>
       <c r="AM131" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="AN131" s="3">
         <v>0.0</v>
@@ -20347,7 +21811,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>63</v>
@@ -20367,13 +21831,13 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>96</v>
@@ -20382,12 +21846,12 @@
         <v>53</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>63</v>
@@ -20407,7 +21871,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>63</v>
@@ -20427,7 +21891,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>63</v>
@@ -20456,13 +21920,13 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I137" s="2" t="s">
         <v>69</v>
@@ -20485,7 +21949,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>63</v>
@@ -20545,7 +22009,7 @@
         <v>0.0</v>
       </c>
       <c r="AM138" s="1" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="AN138" s="3">
         <v>2.0</v>
@@ -20735,7 +22199,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>99</v>
@@ -20755,7 +22219,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>99</v>
@@ -20775,7 +22239,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>99</v>
@@ -20798,7 +22262,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>99</v>
@@ -20827,7 +22291,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>99</v>
@@ -20836,13 +22300,13 @@
         <v>92</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>81</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="M6" s="3">
         <v>3.0</v>
@@ -20856,7 +22320,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>99</v>
@@ -20910,7 +22374,7 @@
         <v>0.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="AN7" s="3">
         <v>2.0</v>
@@ -20942,7 +22406,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>49</v>
@@ -20962,7 +22426,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>49</v>
@@ -20982,7 +22446,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>49</v>
@@ -21011,7 +22475,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -21040,7 +22504,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>49</v>
@@ -21094,7 +22558,7 @@
         <v>0.0</v>
       </c>
       <c r="AM12" s="1" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="AN12" s="3">
         <v>2.0</v>
@@ -21126,7 +22590,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>63</v>
@@ -21146,7 +22610,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>63</v>
@@ -21166,13 +22630,13 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>55</v>
@@ -21198,7 +22662,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>63</v>
@@ -21252,7 +22716,7 @@
         <v>1.0</v>
       </c>
       <c r="AM16" s="1" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="AN16" s="3">
         <v>1.0</v>
@@ -21284,7 +22748,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>74</v>
@@ -21304,7 +22768,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>74</v>
@@ -21324,7 +22788,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>74</v>
@@ -21340,10 +22804,10 @@
         <v>55</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="N19" s="1" t="b">
         <v>1</v>
@@ -21351,7 +22815,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>74</v>
@@ -21384,7 +22848,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>74</v>
@@ -21445,7 +22909,7 @@
         <v>0.0</v>
       </c>
       <c r="AM21" s="1" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="AN21" s="3">
         <v>1.0</v>
@@ -21477,7 +22941,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>80</v>
@@ -21497,7 +22961,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>80</v>
@@ -21517,13 +22981,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>55</v>
@@ -21546,7 +23010,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>80</v>
@@ -21606,7 +23070,7 @@
         <v>0.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="AN25" s="3">
         <v>1.0</v>
@@ -21638,7 +23102,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>85</v>
@@ -21658,7 +23122,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>85</v>
@@ -21678,13 +23142,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>53</v>
@@ -21707,7 +23171,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>85</v>
@@ -21730,7 +23194,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>85</v>
@@ -21790,7 +23254,7 @@
         <v>0.0</v>
       </c>
       <c r="AM30" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="AN30" s="3">
         <v>1.0</v>
@@ -21822,7 +23286,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>95</v>
@@ -21842,7 +23306,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>95</v>
@@ -21862,7 +23326,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>95</v>
@@ -21872,7 +23336,7 @@
       <c r="E33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>55</v>
@@ -21889,7 +23353,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>95</v>
@@ -21899,7 +23363,7 @@
       <c r="E34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>53</v>
@@ -21916,7 +23380,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>95</v>
@@ -21929,7 +23393,7 @@
         <v>0.0</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>106</v>
@@ -21980,7 +23444,7 @@
         <v>0.0</v>
       </c>
       <c r="AM35" s="1" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="AN35" s="3">
         <v>0.0</v>
@@ -22012,7 +23476,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>99</v>
@@ -22032,7 +23496,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>99</v>
@@ -22052,13 +23516,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>59</v>
@@ -22081,7 +23545,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>99</v>
@@ -22141,7 +23605,7 @@
         <v>0.0</v>
       </c>
       <c r="AM39" s="1" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="AN39" s="3">
         <v>1.0</v>
@@ -22173,7 +23637,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>49</v>
@@ -22193,13 +23657,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>55</v>
@@ -22216,13 +23680,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>53</v>
@@ -22245,7 +23709,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>49</v>
@@ -22299,7 +23763,7 @@
         <v>3.0</v>
       </c>
       <c r="AM43" s="1" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="AN43" s="3">
         <v>1.0</v>
@@ -22331,7 +23795,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>63</v>
@@ -22351,7 +23815,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>63</v>
@@ -22371,13 +23835,13 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>55</v>
@@ -22400,13 +23864,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>53</v>
@@ -22429,7 +23893,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>63</v>
@@ -22483,7 +23947,7 @@
         <v>0.0</v>
       </c>
       <c r="AM48" s="1" t="s">
-        <v>203</v>
+        <v>123</v>
       </c>
       <c r="AN48" s="3">
         <v>2.0</v>
@@ -22515,7 +23979,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>74</v>
@@ -22535,7 +23999,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>74</v>
@@ -22567,7 +24031,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>74</v>
@@ -22630,7 +24094,7 @@
         <v>0.0</v>
       </c>
       <c r="AM51" s="1" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="AN51" s="3">
         <v>1.0</v>
@@ -22662,7 +24126,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>80</v>
@@ -22682,7 +24146,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>80</v>
@@ -22702,13 +24166,13 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>53</v>
@@ -22731,7 +24195,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>80</v>
@@ -22785,7 +24249,7 @@
         <v>2.0</v>
       </c>
       <c r="AM55" s="1" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="AN55" s="3">
         <v>1.0</v>
@@ -22817,7 +24281,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>85</v>
@@ -22837,7 +24301,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>85</v>
@@ -22857,13 +24321,13 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>53</v>
@@ -22886,7 +24350,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>85</v>
@@ -22940,7 +24404,7 @@
         <v>0.0</v>
       </c>
       <c r="AM59" s="1" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="AN59" s="3">
         <v>1.0</v>
@@ -22972,7 +24436,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>95</v>
@@ -22992,7 +24456,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>95</v>
@@ -23012,7 +24476,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>95</v>
@@ -23066,7 +24530,7 @@
         <v>0.0</v>
       </c>
       <c r="AM62" s="1" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="AN62" s="3">
         <v>0.0</v>
@@ -23098,7 +24562,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>99</v>
@@ -23118,7 +24582,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>99</v>
@@ -23138,16 +24602,16 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>81</v>
@@ -23170,7 +24634,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>99</v>
@@ -23224,7 +24688,7 @@
         <v>0.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="AN66" s="3">
         <v>1.0</v>
@@ -23256,7 +24720,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>49</v>
@@ -23276,7 +24740,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>49</v>
@@ -23296,13 +24760,13 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>53</v>
@@ -23325,7 +24789,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>49</v>
@@ -23379,7 +24843,7 @@
         <v>0.0</v>
       </c>
       <c r="AM70" s="1" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="AN70" s="3">
         <v>1.0</v>
@@ -23411,7 +24875,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>63</v>
@@ -23431,7 +24895,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>63</v>
@@ -23451,7 +24915,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>63</v>
@@ -23480,7 +24944,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>63</v>
@@ -23534,7 +24998,7 @@
         <v>0.0</v>
       </c>
       <c r="AM74" s="1" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="AN74" s="3">
         <v>1.0</v>
@@ -23566,7 +25030,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>74</v>
@@ -23586,7 +25050,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>74</v>
@@ -23606,13 +25070,13 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>74</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>55</v>
@@ -23635,7 +25099,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>74</v>
@@ -23658,7 +25122,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>74</v>
@@ -23712,7 +25176,7 @@
         <v>1.0</v>
       </c>
       <c r="AM79" s="1" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="AN79" s="3">
         <v>1.0</v>
@@ -23744,7 +25208,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>80</v>
@@ -23764,13 +25228,13 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>56</v>
@@ -23793,7 +25257,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>80</v>
@@ -23853,7 +25317,7 @@
         <v>0.0</v>
       </c>
       <c r="AM82" s="1" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="AN82" s="3">
         <v>1.0</v>
@@ -23885,7 +25349,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>85</v>
@@ -23905,7 +25369,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>85</v>
@@ -23925,7 +25389,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>85</v>
@@ -23954,13 +25418,13 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>56</v>
@@ -23983,7 +25447,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>85</v>
@@ -24043,7 +25507,7 @@
         <v>0.0</v>
       </c>
       <c r="AM87" s="1" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="AN87" s="3">
         <v>2.0</v>
@@ -24075,7 +25539,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>95</v>
@@ -24095,7 +25559,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>95</v>
@@ -24115,7 +25579,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>95</v>
@@ -24144,7 +25608,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>95</v>
@@ -24198,7 +25662,7 @@
         <v>1.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="AN91" s="3">
         <v>1.0</v>
@@ -24230,7 +25694,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>99</v>
@@ -24250,7 +25714,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>99</v>
@@ -24270,7 +25734,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>99</v>
@@ -24299,7 +25763,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>99</v>
@@ -24353,7 +25817,7 @@
         <v>0.0</v>
       </c>
       <c r="AM95" s="1" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="AN95" s="3">
         <v>1.0</v>
@@ -24385,7 +25849,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>49</v>
@@ -24405,7 +25869,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>49</v>
@@ -24425,13 +25889,13 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>55</v>
@@ -24454,7 +25918,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>49</v>
@@ -24483,7 +25947,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>49</v>
@@ -24537,7 +26001,7 @@
         <v>0.0</v>
       </c>
       <c r="AM100" s="1" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="AN100" s="3">
         <v>2.0</v>
@@ -24569,7 +26033,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>63</v>
@@ -24589,7 +26053,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>63</v>
@@ -24609,7 +26073,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>63</v>
@@ -24638,7 +26102,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>63</v>
@@ -24692,7 +26156,7 @@
         <v>2.0</v>
       </c>
       <c r="AM104" s="1" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="AN104" s="3">
         <v>1.0</v>
@@ -24724,7 +26188,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>74</v>
@@ -24744,7 +26208,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>74</v>
@@ -24764,7 +26228,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>74</v>
@@ -24776,7 +26240,7 @@
         <v>96</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="L107" s="2" t="s">
         <v>52</v>
@@ -24793,7 +26257,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>74</v>
@@ -24822,7 +26286,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>74</v>
@@ -24882,7 +26346,7 @@
         <v>2.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="AN109" s="3">
         <v>2.0</v>
@@ -24914,7 +26378,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>80</v>
@@ -24934,7 +26398,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>80</v>
@@ -24954,7 +26418,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>80</v>
@@ -24977,7 +26441,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>80</v>
@@ -25006,7 +26470,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>80</v>
@@ -25060,7 +26524,7 @@
         <v>0.0</v>
       </c>
       <c r="AM114" s="1" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="AN114" s="3">
         <v>1.0</v>
@@ -25092,7 +26556,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>85</v>
@@ -25112,7 +26576,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>85</v>
@@ -25132,7 +26596,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>85</v>
@@ -25152,7 +26616,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>85</v>
@@ -25181,7 +26645,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>85</v>
@@ -25238,7 +26702,7 @@
         <v>0.0</v>
       </c>
       <c r="AM119" s="1" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="AN119" s="3">
         <v>1.0</v>
@@ -25270,7 +26734,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>95</v>
@@ -25290,7 +26754,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>95</v>
@@ -25310,7 +26774,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>95</v>
@@ -25339,7 +26803,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>95</v>
@@ -25362,7 +26826,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>95</v>
@@ -25419,7 +26883,7 @@
         <v>1.0</v>
       </c>
       <c r="AM124" s="1" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="AN124" s="3">
         <v>1.0</v>
@@ -25451,7 +26915,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>99</v>
@@ -25471,7 +26935,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>99</v>
@@ -25491,7 +26955,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>99</v>
@@ -25511,7 +26975,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>99</v>
@@ -25540,7 +27004,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>99</v>
@@ -25600,7 +27064,7 @@
         <v>1.0</v>
       </c>
       <c r="AM129" s="1" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="AN129" s="3">
         <v>1.0</v>
@@ -25632,7 +27096,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>49</v>
@@ -25652,7 +27116,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>49</v>
@@ -25672,7 +27136,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>49</v>
@@ -25692,13 +27156,13 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="I133" s="2" t="s">
         <v>55</v>
@@ -25721,13 +27185,13 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I134" s="2" t="s">
         <v>53</v>
@@ -25750,7 +27214,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>49</v>
@@ -25804,7 +27268,7 @@
         <v>0.0</v>
       </c>
       <c r="AM135" s="1" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="AN135" s="3">
         <v>2.0</v>
@@ -25836,7 +27300,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>63</v>
@@ -25856,7 +27320,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>63</v>
@@ -25876,7 +27340,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>63</v>
@@ -25896,7 +27360,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>63</v>
@@ -25925,13 +27389,13 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I140" s="2" t="s">
         <v>53</v>
@@ -25954,7 +27418,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>63</v>
@@ -26008,7 +27472,7 @@
         <v>0.0</v>
       </c>
       <c r="AM141" s="1" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="AN141" s="3">
         <v>2.0</v>

--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Bolevec/Databaze Bolevec 2026.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Bolevec/Databaze Bolevec 2026.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4107" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4153" uniqueCount="378">
   <si>
     <t>Datum</t>
   </si>
@@ -415,6 +415,18 @@
   </si>
   <si>
     <t>9 min 44 s</t>
+  </si>
+  <si>
+    <t>20.05.2026</t>
+  </si>
+  <si>
+    <t>9 min 19 s</t>
+  </si>
+  <si>
+    <t>21.05.2026</t>
+  </si>
+  <si>
+    <t>7 min 07 s</t>
   </si>
   <si>
     <t>01.04.2026</t>
@@ -4972,6 +4984,337 @@
         <v>0.0</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M90" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N90" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O90" s="3">
+        <v>45.0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L91" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M91" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N91" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O91" s="3">
+        <v>180.0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q92" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R92" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S92" s="3">
+        <v>5041.98</v>
+      </c>
+      <c r="T92" s="3">
+        <v>750.0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>1683.25</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X92" s="3">
+        <v>607.0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>3015.0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>2365.0</v>
+      </c>
+      <c r="AB92" s="3">
+        <v>13080.63</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>-0.3999999999996362</v>
+      </c>
+      <c r="AD92" s="3">
+        <v>0.6610012889534052</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>225.0</v>
+      </c>
+      <c r="AJ92" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL92" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM92" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN92" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AO92" s="3">
+        <v>47.0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="AR92" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS92" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT92" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU92" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV92" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="M94" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N94" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O94" s="3">
+        <v>315.0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="P95" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q95" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R95" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="S95" s="3">
+        <v>4199.28</v>
+      </c>
+      <c r="T95" s="3">
+        <v>563.0</v>
+      </c>
+      <c r="U95" s="3">
+        <v>4914.75</v>
+      </c>
+      <c r="V95" s="3">
+        <v>1199.0</v>
+      </c>
+      <c r="W95" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X95" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y95" s="3">
+        <v>3744.0</v>
+      </c>
+      <c r="AA95" s="3">
+        <v>2538.0</v>
+      </c>
+      <c r="AB95" s="3">
+        <v>17472.63</v>
+      </c>
+      <c r="AC95" s="3">
+        <v>0.3999999999978172</v>
+      </c>
+      <c r="AD95" s="3">
+        <v>0.6436904169734367</v>
+      </c>
+      <c r="AI95" s="3">
+        <v>315.0</v>
+      </c>
+      <c r="AJ95" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK95" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL95" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM95" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AN95" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO95" s="3">
+        <v>54.0</v>
+      </c>
+      <c r="AP95" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="AQ95" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AR95" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS95" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT95" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU95" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV95" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -5132,7 +5475,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>95</v>
@@ -5152,7 +5495,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>95</v>
@@ -5172,13 +5515,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>55</v>
@@ -5192,7 +5535,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>95</v>
@@ -5204,10 +5547,10 @@
         <v>55</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="M5" s="3">
         <v>5.0</v>
@@ -5221,7 +5564,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>95</v>
@@ -5281,7 +5624,7 @@
         <v>0.0</v>
       </c>
       <c r="AM6" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AN6" s="3">
         <v>1.0</v>
@@ -5313,7 +5656,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>99</v>
@@ -5333,13 +5676,13 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>53</v>
@@ -5353,7 +5696,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>99</v>
@@ -5382,7 +5725,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>99</v>
@@ -5411,7 +5754,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>99</v>
@@ -5471,7 +5814,7 @@
         <v>0.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AN11" s="3">
         <v>2.0</v>
@@ -5503,7 +5846,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>49</v>
@@ -5515,7 +5858,7 @@
         <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>67</v>
@@ -5523,13 +5866,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>55</v>
@@ -5543,7 +5886,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>49</v>
@@ -5563,7 +5906,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>49</v>
@@ -5592,7 +5935,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>49</v>
@@ -5621,7 +5964,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>49</v>
@@ -5684,7 +6027,7 @@
         <v>0.0</v>
       </c>
       <c r="AM17" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="AN17" s="3">
         <v>2.0</v>
@@ -5716,7 +6059,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>63</v>
@@ -5736,13 +6079,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>55</v>
@@ -5756,7 +6099,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>63</v>
@@ -5776,7 +6119,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>63</v>
@@ -5796,7 +6139,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>63</v>
@@ -5825,7 +6168,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>63</v>
@@ -5854,7 +6197,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>63</v>
@@ -5914,7 +6257,7 @@
         <v>0.0</v>
       </c>
       <c r="AM24" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="AN24" s="3">
         <v>2.0</v>
@@ -5946,7 +6289,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>74</v>
@@ -5966,7 +6309,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>74</v>
@@ -5998,7 +6341,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>74</v>
@@ -6058,7 +6401,7 @@
         <v>0.0</v>
       </c>
       <c r="AM27" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="AN27" s="3">
         <v>1.0</v>
@@ -6090,7 +6433,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>80</v>
@@ -6110,13 +6453,13 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>55</v>
@@ -6130,7 +6473,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>80</v>
@@ -6150,7 +6493,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>80</v>
@@ -6183,7 +6526,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>80</v>
@@ -6196,7 +6539,7 @@
         <v>92</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>81</v>
@@ -6210,7 +6553,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>80</v>
@@ -6226,7 +6569,7 @@
         <v>53</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>107</v>
@@ -6243,7 +6586,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>80</v>
@@ -6307,7 +6650,7 @@
         <v>0.0</v>
       </c>
       <c r="AM34" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AN34" s="3">
         <v>2.0</v>
@@ -6339,7 +6682,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>85</v>
@@ -6351,7 +6694,7 @@
         <v>51</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>114</v>
@@ -6359,7 +6702,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>85</v>
@@ -6379,7 +6722,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>85</v>
@@ -6399,7 +6742,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>85</v>
@@ -6422,7 +6765,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>85</v>
@@ -6451,7 +6794,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>85</v>
@@ -6511,7 +6854,7 @@
         <v>0.0</v>
       </c>
       <c r="AM40" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AN40" s="3">
         <v>1.0</v>
@@ -6543,7 +6886,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>95</v>
@@ -6563,13 +6906,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>55</v>
@@ -6583,7 +6926,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>95</v>
@@ -6603,7 +6946,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>95</v>
@@ -6612,7 +6955,7 @@
         <v>92</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>81</v>
@@ -6626,7 +6969,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>95</v>
@@ -6683,7 +7026,7 @@
         <v>0.0</v>
       </c>
       <c r="AM45" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="AN45" s="3">
         <v>0.0</v>
@@ -6715,7 +7058,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>99</v>
@@ -6735,13 +7078,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>55</v>
@@ -6755,7 +7098,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>99</v>
@@ -6784,7 +7127,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>99</v>
@@ -6844,7 +7187,7 @@
         <v>0.0</v>
       </c>
       <c r="AM49" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AN49" s="3">
         <v>1.0</v>
@@ -6876,7 +7219,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>49</v>
@@ -6888,7 +7231,7 @@
         <v>51</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>108</v>
@@ -6896,16 +7239,16 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>86</v>
@@ -6916,7 +7259,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>49</v>
@@ -6936,7 +7279,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>49</v>
@@ -6948,7 +7291,7 @@
         <v>55</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>90</v>
@@ -6965,7 +7308,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>49</v>
@@ -6974,7 +7317,7 @@
         <v>58</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>52</v>
@@ -6994,7 +7337,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>49</v>
@@ -7086,7 +7429,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>63</v>
@@ -7106,19 +7449,19 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>108</v>
@@ -7126,7 +7469,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>63</v>
@@ -7138,7 +7481,7 @@
         <v>53</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>65</v>
@@ -7146,7 +7489,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>63</v>
@@ -7169,7 +7512,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>63</v>
@@ -7198,7 +7541,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>63</v>
@@ -7261,7 +7604,7 @@
         <v>3.0</v>
       </c>
       <c r="AM61" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="AN61" s="3">
         <v>1.0</v>
@@ -7293,7 +7636,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>74</v>
@@ -7313,13 +7656,13 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>55</v>
@@ -7333,7 +7676,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>74</v>
@@ -7353,7 +7696,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>74</v>
@@ -7382,7 +7725,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>74</v>
@@ -7411,7 +7754,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>74</v>
@@ -7471,7 +7814,7 @@
         <v>0.0</v>
       </c>
       <c r="AM67" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AN67" s="3">
         <v>2.0</v>
@@ -7503,7 +7846,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>80</v>
@@ -7515,7 +7858,7 @@
         <v>51</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>114</v>
@@ -7523,13 +7866,13 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>87</v>
@@ -7543,7 +7886,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>80</v>
@@ -7563,7 +7906,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>80</v>
@@ -7592,7 +7935,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>80</v>
@@ -7655,7 +7998,7 @@
         <v>0.0</v>
       </c>
       <c r="AM72" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="AN72" s="3">
         <v>1.0</v>
@@ -7687,7 +8030,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>85</v>
@@ -7707,13 +8050,13 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>55</v>
@@ -7727,7 +8070,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>85</v>
@@ -7747,7 +8090,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>85</v>
@@ -7765,7 +8108,7 @@
         <v>121</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="M76" s="3">
         <v>2.0</v>
@@ -7779,7 +8122,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>85</v>
@@ -7839,7 +8182,7 @@
         <v>0.0</v>
       </c>
       <c r="AM77" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="AN77" s="3">
         <v>1.0</v>
@@ -7871,7 +8214,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>95</v>
@@ -7891,7 +8234,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>95</v>
@@ -7911,7 +8254,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>95</v>
@@ -7934,7 +8277,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>95</v>
@@ -7963,7 +8306,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>95</v>
@@ -8023,7 +8366,7 @@
         <v>0.0</v>
       </c>
       <c r="AM82" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="AN82" s="3">
         <v>1.0</v>
@@ -8055,7 +8398,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>99</v>
@@ -8075,7 +8418,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>99</v>
@@ -8095,7 +8438,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>99</v>
@@ -8107,7 +8450,7 @@
         <v>59</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>67</v>
@@ -8124,7 +8467,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>99</v>
@@ -8187,7 +8530,7 @@
         <v>0.0</v>
       </c>
       <c r="AM86" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="AN86" s="3">
         <v>1.0</v>
@@ -8219,7 +8562,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>49</v>
@@ -8231,7 +8574,7 @@
         <v>51</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>67</v>
@@ -8239,7 +8582,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>49</v>
@@ -8259,7 +8602,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>49</v>
@@ -8288,7 +8631,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>49</v>
@@ -8317,7 +8660,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>49</v>
@@ -8377,7 +8720,7 @@
         <v>0.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AN91" s="3">
         <v>2.0</v>
@@ -8409,7 +8752,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>63</v>
@@ -8429,7 +8772,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>63</v>
@@ -8458,7 +8801,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>63</v>
@@ -8487,7 +8830,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>63</v>
@@ -8541,7 +8884,7 @@
         <v>0.0</v>
       </c>
       <c r="AM95" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AN95" s="3">
         <v>2.0</v>
@@ -8573,7 +8916,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>74</v>
@@ -8593,7 +8936,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>74</v>
@@ -8622,7 +8965,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>74</v>
@@ -8676,7 +9019,7 @@
         <v>1.0</v>
       </c>
       <c r="AM98" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AN98" s="3">
         <v>1.0</v>
@@ -8708,7 +9051,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>80</v>
@@ -8728,7 +9071,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>80</v>
@@ -8748,7 +9091,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>80</v>
@@ -8777,7 +9120,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>80</v>
@@ -8831,7 +9174,7 @@
         <v>1.0</v>
       </c>
       <c r="AM102" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="AN102" s="3">
         <v>1.0</v>
@@ -8863,7 +9206,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>85</v>
@@ -8883,7 +9226,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>85</v>
@@ -8903,7 +9246,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>85</v>
@@ -8932,7 +9275,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>85</v>
@@ -8944,7 +9287,7 @@
         <v>59</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="L106" s="2" t="s">
         <v>67</v>
@@ -8961,7 +9304,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>85</v>
@@ -9021,7 +9364,7 @@
         <v>0.0</v>
       </c>
       <c r="AM107" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="AN107" s="3">
         <v>2.0</v>
@@ -9053,7 +9396,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>95</v>
@@ -9073,7 +9416,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>95</v>
@@ -9093,7 +9436,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>95</v>
@@ -9125,7 +9468,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>95</v>
@@ -9188,7 +9531,7 @@
         <v>0.0</v>
       </c>
       <c r="AM111" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AN111" s="3">
         <v>1.0</v>
@@ -9220,7 +9563,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>99</v>
@@ -9240,7 +9583,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>99</v>
@@ -9260,7 +9603,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>99</v>
@@ -9289,7 +9632,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>99</v>
@@ -9352,7 +9695,7 @@
         <v>2.0</v>
       </c>
       <c r="AM115" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="AN115" s="3">
         <v>1.0</v>
@@ -9384,7 +9727,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>49</v>
@@ -9404,7 +9747,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>49</v>
@@ -9427,7 +9770,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>49</v>
@@ -9447,7 +9790,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>49</v>
@@ -9476,7 +9819,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>49</v>
@@ -9505,7 +9848,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>49</v>
@@ -9565,7 +9908,7 @@
         <v>2.0</v>
       </c>
       <c r="AM121" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AN121" s="3">
         <v>2.0</v>
@@ -9597,7 +9940,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>63</v>
@@ -9609,7 +9952,7 @@
         <v>51</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>108</v>
@@ -9617,7 +9960,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>63</v>
@@ -9637,7 +9980,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>63</v>
@@ -9666,7 +10009,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>63</v>
@@ -9695,7 +10038,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>63</v>
@@ -9758,7 +10101,7 @@
         <v>1.0</v>
       </c>
       <c r="AM126" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="AN126" s="3">
         <v>2.0</v>
@@ -9790,7 +10133,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>74</v>
@@ -9810,7 +10153,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>74</v>
@@ -9830,7 +10173,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>74</v>
@@ -9859,7 +10202,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>74</v>
@@ -9888,7 +10231,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>74</v>
@@ -9948,7 +10291,7 @@
         <v>0.0</v>
       </c>
       <c r="AM131" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AN131" s="3">
         <v>2.0</v>
@@ -9980,7 +10323,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>80</v>
@@ -10000,7 +10343,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>80</v>
@@ -10020,7 +10363,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>80</v>
@@ -10052,7 +10395,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>80</v>
@@ -10112,7 +10455,7 @@
         <v>0.0</v>
       </c>
       <c r="AM135" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AN135" s="3">
         <v>1.0</v>
@@ -10144,7 +10487,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>85</v>
@@ -10156,7 +10499,7 @@
         <v>51</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>55</v>
@@ -10164,7 +10507,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>85</v>
@@ -10184,7 +10527,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>85</v>
@@ -10207,7 +10550,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>85</v>
@@ -10216,7 +10559,7 @@
         <v>91</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>81</v>
@@ -10236,7 +10579,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>85</v>
@@ -10296,7 +10639,7 @@
         <v>1.0</v>
       </c>
       <c r="AM140" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="AN140" s="3">
         <v>1.0</v>
@@ -10328,7 +10671,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>95</v>
@@ -10348,7 +10691,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>95</v>
@@ -10357,13 +10700,13 @@
         <v>68</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>81</v>
       </c>
       <c r="L142" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="M142" s="3">
         <v>9.0</v>
@@ -10377,7 +10720,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>95</v>
@@ -10431,7 +10774,7 @@
         <v>3.0</v>
       </c>
       <c r="AM143" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="AN143" s="3">
         <v>1.0</v>
@@ -10463,7 +10806,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>99</v>
@@ -10483,7 +10826,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>99</v>
@@ -10515,7 +10858,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>99</v>
@@ -10544,7 +10887,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>99</v>
@@ -10598,7 +10941,7 @@
         <v>0.0</v>
       </c>
       <c r="AM147" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AN147" s="3">
         <v>2.0</v>
@@ -10788,7 +11131,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>74</v>
@@ -10808,7 +11151,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>74</v>
@@ -10820,7 +11163,7 @@
         <v>82</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>107</v>
@@ -10828,7 +11171,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>74</v>
@@ -10848,7 +11191,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>74</v>
@@ -10877,7 +11220,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>74</v>
@@ -10937,7 +11280,7 @@
         <v>0.0</v>
       </c>
       <c r="AM6" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AN6" s="3">
         <v>1.0</v>
@@ -10969,7 +11312,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>80</v>
@@ -10984,18 +11327,18 @@
         <v>81</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>55</v>
@@ -11009,7 +11352,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>80</v>
@@ -11029,13 +11372,13 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>53</v>
@@ -11049,7 +11392,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>80</v>
@@ -11061,7 +11404,7 @@
         <v>55</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>90</v>
@@ -11078,16 +11421,16 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>81</v>
@@ -11107,7 +11450,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>80</v>
@@ -11167,7 +11510,7 @@
         <v>1.0</v>
       </c>
       <c r="AM13" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AN13" s="3">
         <v>2.0</v>
@@ -11199,7 +11542,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>85</v>
@@ -11214,18 +11557,18 @@
         <v>81</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -11239,7 +11582,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>85</v>
@@ -11254,7 +11597,7 @@
         <v>88</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>67</v>
@@ -11262,7 +11605,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>85</v>
@@ -11291,7 +11634,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>85</v>
@@ -11320,7 +11663,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>85</v>
@@ -11380,7 +11723,7 @@
         <v>0.0</v>
       </c>
       <c r="AM19" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AN19" s="3">
         <v>2.0</v>
@@ -11412,7 +11755,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>95</v>
@@ -11424,7 +11767,7 @@
         <v>51</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>55</v>
@@ -11432,7 +11775,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>95</v>
@@ -11452,13 +11795,13 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>53</v>
@@ -11472,13 +11815,13 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>55</v>
@@ -11501,7 +11844,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>95</v>
@@ -11530,7 +11873,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>95</v>
@@ -11590,7 +11933,7 @@
         <v>0.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="AN25" s="3">
         <v>2.0</v>
@@ -11622,7 +11965,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>99</v>
@@ -11642,7 +11985,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>99</v>
@@ -11662,13 +12005,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>55</v>
@@ -11691,7 +12034,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>99</v>
@@ -11783,7 +12126,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>49</v>
@@ -11795,7 +12138,7 @@
         <v>122</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>51</v>
@@ -11803,7 +12146,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>49</v>
@@ -11823,13 +12166,13 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>96</v>
@@ -11838,24 +12181,24 @@
         <v>53</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>70</v>
@@ -11863,19 +12206,19 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>55</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>90</v>
@@ -11886,13 +12229,13 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>53</v>
@@ -11915,7 +12258,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>49</v>
@@ -11975,7 +12318,7 @@
         <v>0.0</v>
       </c>
       <c r="AM36" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AN36" s="3">
         <v>1.0</v>
@@ -12007,7 +12350,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>63</v>
@@ -12027,7 +12370,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>63</v>
@@ -12047,7 +12390,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>63</v>
@@ -12076,7 +12419,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>63</v>
@@ -12105,7 +12448,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>63</v>
@@ -12165,7 +12508,7 @@
         <v>1.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AN41" s="3">
         <v>2.0</v>
@@ -12197,7 +12540,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>74</v>
@@ -12217,7 +12560,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>74</v>
@@ -12229,7 +12572,7 @@
         <v>87</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>87</v>
@@ -12237,7 +12580,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>74</v>
@@ -12266,19 +12609,19 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>74</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>100</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>70</v>
@@ -12289,7 +12632,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>74</v>
@@ -12349,7 +12692,7 @@
         <v>0.0</v>
       </c>
       <c r="AM46" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AN46" s="3">
         <v>1.0</v>
@@ -12381,7 +12724,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>80</v>
@@ -12401,13 +12744,13 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>55</v>
@@ -12424,13 +12767,13 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>59</v>
@@ -12453,7 +12796,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>80</v>
@@ -12507,7 +12850,7 @@
         <v>0.0</v>
       </c>
       <c r="AM50" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="AN50" s="3">
         <v>1.0</v>
@@ -12539,7 +12882,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>85</v>
@@ -12559,27 +12902,27 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>56</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>85</v>
@@ -12599,13 +12942,13 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>55</v>
@@ -12622,13 +12965,13 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>53</v>
@@ -12651,7 +12994,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>85</v>
@@ -12714,7 +13057,7 @@
         <v>1.0</v>
       </c>
       <c r="AM56" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AN56" s="3">
         <v>1.0</v>
@@ -12746,7 +13089,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>95</v>
@@ -12766,7 +13109,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>95</v>
@@ -12786,13 +13129,13 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>56</v>
@@ -12806,13 +13149,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>55</v>
@@ -12829,7 +13172,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>95</v>
@@ -12858,7 +13201,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>95</v>
@@ -12918,7 +13261,7 @@
         <v>0.0</v>
       </c>
       <c r="AM62" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AN62" s="3">
         <v>1.0</v>
@@ -12950,7 +13293,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>99</v>
@@ -12962,7 +13305,7 @@
         <v>51</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>108</v>
@@ -12970,7 +13313,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>99</v>
@@ -12990,19 +13333,19 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>70</v>
@@ -13010,13 +13353,13 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>55</v>
@@ -13039,7 +13382,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>99</v>
@@ -13099,7 +13442,7 @@
         <v>0.0</v>
       </c>
       <c r="AM67" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AN67" s="3">
         <v>1.0</v>
@@ -13131,7 +13474,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>49</v>
@@ -13143,7 +13486,7 @@
         <v>51</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>108</v>
@@ -13151,7 +13494,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>49</v>
@@ -13163,7 +13506,7 @@
         <v>53</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>65</v>
@@ -13171,13 +13514,13 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>53</v>
@@ -13186,24 +13529,24 @@
         <v>64</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>55</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>114</v>
@@ -13220,7 +13563,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>49</v>
@@ -13249,7 +13592,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>49</v>
@@ -13309,7 +13652,7 @@
         <v>0.0</v>
       </c>
       <c r="AM73" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="AN73" s="3">
         <v>2.0</v>
@@ -13341,7 +13684,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>63</v>
@@ -13361,13 +13704,13 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>55</v>
@@ -13381,7 +13724,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>63</v>
@@ -13393,7 +13736,7 @@
         <v>59</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>122</v>
@@ -13401,7 +13744,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>63</v>
@@ -13424,7 +13767,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>63</v>
@@ -13453,7 +13796,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>63</v>
@@ -13482,7 +13825,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>63</v>
@@ -13542,7 +13885,7 @@
         <v>0.0</v>
       </c>
       <c r="AM80" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="AN80" s="3">
         <v>2.0</v>
@@ -13574,7 +13917,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>74</v>
@@ -13594,7 +13937,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>74</v>
@@ -13623,7 +13966,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>74</v>
@@ -13652,7 +13995,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>74</v>
@@ -13709,7 +14052,7 @@
         <v>0.0</v>
       </c>
       <c r="AM84" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="AN84" s="3">
         <v>2.0</v>
@@ -13741,7 +14084,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>80</v>
@@ -13753,7 +14096,7 @@
         <v>51</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>114</v>
@@ -13761,13 +14104,13 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>55</v>
@@ -13781,7 +14124,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>80</v>
@@ -13801,19 +14144,19 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>70</v>
@@ -13821,13 +14164,13 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>55</v>
@@ -13844,19 +14187,19 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>114</v>
@@ -13867,7 +14210,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>80</v>
@@ -13927,7 +14270,7 @@
         <v>0.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AN91" s="3">
         <v>0.0</v>
@@ -13959,7 +14302,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>85</v>
@@ -13979,13 +14322,13 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>55</v>
@@ -13999,7 +14342,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>85</v>
@@ -14019,19 +14362,19 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>114</v>
@@ -14039,7 +14382,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>85</v>
@@ -14068,13 +14411,13 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>53</v>
@@ -14097,7 +14440,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>85</v>
@@ -14157,7 +14500,7 @@
         <v>0.0</v>
       </c>
       <c r="AM98" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AN98" s="3">
         <v>2.0</v>
@@ -14189,7 +14532,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>95</v>
@@ -14209,7 +14552,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>95</v>
@@ -14229,19 +14572,19 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>70</v>
@@ -14249,7 +14592,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>95</v>
@@ -14269,13 +14612,13 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>55</v>
@@ -14298,7 +14641,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>95</v>
@@ -14327,7 +14670,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>95</v>
@@ -14384,7 +14727,7 @@
         <v>1.0</v>
       </c>
       <c r="AM105" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="AN105" s="3">
         <v>2.0</v>
@@ -14416,7 +14759,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>99</v>
@@ -14436,13 +14779,13 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>55</v>
@@ -14456,13 +14799,13 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>55</v>
@@ -14485,7 +14828,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>99</v>
@@ -14542,7 +14885,7 @@
         <v>0.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="AN109" s="3">
         <v>1.0</v>
@@ -14574,7 +14917,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>49</v>
@@ -14594,13 +14937,13 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>55</v>
@@ -14614,7 +14957,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>49</v>
@@ -14634,13 +14977,13 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I113" s="2" t="s">
         <v>55</v>
@@ -14663,7 +15006,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>49</v>
@@ -14692,7 +15035,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>49</v>
@@ -14749,7 +15092,7 @@
         <v>0.0</v>
       </c>
       <c r="AM115" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="AN115" s="3">
         <v>2.0</v>
@@ -14781,7 +15124,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>63</v>
@@ -14801,7 +15144,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>63</v>
@@ -14821,19 +15164,19 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>70</v>
@@ -14841,7 +15184,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>63</v>
@@ -14870,7 +15213,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>63</v>
@@ -14899,7 +15242,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>63</v>
@@ -14959,7 +15302,7 @@
         <v>0.0</v>
       </c>
       <c r="AM121" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AN121" s="3">
         <v>2.0</v>
@@ -14991,7 +15334,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>74</v>
@@ -15011,7 +15354,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>74</v>
@@ -15034,13 +15377,13 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>74</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I124" s="2" t="s">
         <v>53</v>
@@ -15063,7 +15406,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>74</v>
@@ -15123,7 +15466,7 @@
         <v>0.0</v>
       </c>
       <c r="AM125" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AN125" s="3">
         <v>1.0</v>
@@ -15155,7 +15498,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>80</v>
@@ -15175,13 +15518,13 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>55</v>
@@ -15195,7 +15538,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>80</v>
@@ -15215,13 +15558,13 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I129" s="2" t="s">
         <v>55</v>
@@ -15244,7 +15587,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>80</v>
@@ -15256,13 +15599,13 @@
         <v>53</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K130" s="2" t="s">
         <v>70</v>
       </c>
       <c r="L130" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="M130" s="3">
         <v>2.0</v>
@@ -15276,7 +15619,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>80</v>
@@ -15336,7 +15679,7 @@
         <v>0.0</v>
       </c>
       <c r="AM131" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AN131" s="3">
         <v>2.0</v>
@@ -15368,7 +15711,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>85</v>
@@ -15380,7 +15723,7 @@
         <v>51</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>114</v>
@@ -15388,7 +15731,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>85</v>
@@ -15408,33 +15751,33 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I135" s="2" t="s">
         <v>55</v>
@@ -15457,7 +15800,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>85</v>
@@ -15469,7 +15812,7 @@
         <v>59</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="L136" s="2" t="s">
         <v>67</v>
@@ -15480,7 +15823,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>85</v>
@@ -15540,7 +15883,7 @@
         <v>0.0</v>
       </c>
       <c r="AM137" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="AN137" s="3">
         <v>1.0</v>
@@ -15572,7 +15915,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>95</v>
@@ -15592,13 +15935,13 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>55</v>
@@ -15612,7 +15955,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>95</v>
@@ -15632,13 +15975,13 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I141" s="2" t="s">
         <v>55</v>
@@ -15661,7 +16004,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>95</v>
@@ -15690,7 +16033,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>95</v>
@@ -15782,7 +16125,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>99</v>
@@ -15802,13 +16145,13 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>55</v>
@@ -15822,7 +16165,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>99</v>
@@ -15842,7 +16185,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>99</v>
@@ -15865,13 +16208,13 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I148" s="2" t="s">
         <v>53</v>
@@ -15894,7 +16237,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>99</v>
@@ -15954,7 +16297,7 @@
         <v>0.0</v>
       </c>
       <c r="AM149" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AN149" s="3">
         <v>1.0</v>
@@ -15986,7 +16329,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>49</v>
@@ -16009,7 +16352,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>49</v>
@@ -16029,13 +16372,13 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>55</v>
@@ -16049,7 +16392,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>49</v>
@@ -16078,7 +16421,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>49</v>
@@ -16101,7 +16444,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>49</v>
@@ -16130,7 +16473,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>49</v>
@@ -16190,7 +16533,7 @@
         <v>1.0</v>
       </c>
       <c r="AM156" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AN156" s="3">
         <v>2.0</v>
@@ -16222,7 +16565,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>63</v>
@@ -16234,7 +16577,7 @@
         <v>51</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>67</v>
@@ -16242,7 +16585,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>63</v>
@@ -16262,7 +16605,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>63</v>
@@ -16291,7 +16634,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>63</v>
@@ -16320,7 +16663,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>63</v>
@@ -16380,7 +16723,7 @@
         <v>0.0</v>
       </c>
       <c r="AM161" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AN161" s="3">
         <v>2.0</v>
@@ -16412,7 +16755,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>74</v>
@@ -16432,7 +16775,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>74</v>
@@ -16452,7 +16795,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>74</v>
@@ -16481,7 +16824,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>74</v>
@@ -16510,7 +16853,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>74</v>
@@ -16564,7 +16907,7 @@
         <v>0.0</v>
       </c>
       <c r="AM166" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AN166" s="3">
         <v>2.0</v>
@@ -16596,7 +16939,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>80</v>
@@ -16616,7 +16959,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>80</v>
@@ -16636,13 +16979,13 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I169" s="2" t="s">
         <v>55</v>
@@ -16659,7 +17002,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>80</v>
@@ -16671,7 +17014,7 @@
         <v>53</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="L170" s="2" t="s">
         <v>114</v>
@@ -16688,7 +17031,7 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>80</v>
@@ -16748,7 +17091,7 @@
         <v>0.0</v>
       </c>
       <c r="AM171" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="AN171" s="3">
         <v>1.0</v>
@@ -16780,7 +17123,7 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>85</v>
@@ -16795,18 +17138,18 @@
         <v>121</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I173" s="2" t="s">
         <v>55</v>
@@ -16829,7 +17172,7 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>85</v>
@@ -16858,7 +17201,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>85</v>
@@ -16915,7 +17258,7 @@
         <v>1.0</v>
       </c>
       <c r="AM175" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AN175" s="3">
         <v>2.0</v>
@@ -17105,7 +17448,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>74</v>
@@ -17125,7 +17468,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>74</v>
@@ -17145,7 +17488,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>74</v>
@@ -17168,7 +17511,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>74</v>
@@ -17197,7 +17540,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>74</v>
@@ -17251,7 +17594,7 @@
         <v>0.0</v>
       </c>
       <c r="AM6" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AN6" s="3">
         <v>1.0</v>
@@ -17283,7 +17626,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>80</v>
@@ -17303,7 +17646,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>80</v>
@@ -17323,13 +17666,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>53</v>
@@ -17346,7 +17689,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>80</v>
@@ -17406,7 +17749,7 @@
         <v>0.0</v>
       </c>
       <c r="AM10" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="AN10" s="3">
         <v>0.0</v>
@@ -17438,7 +17781,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>85</v>
@@ -17458,16 +17801,16 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="M12" s="3">
         <v>1.0</v>
@@ -17481,7 +17824,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>85</v>
@@ -17544,7 +17887,7 @@
         <v>1.0</v>
       </c>
       <c r="AM13" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AN13" s="3">
         <v>1.0</v>
@@ -17576,7 +17919,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>95</v>
@@ -17596,22 +17939,22 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>55</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="M15" s="3">
         <v>1.0</v>
@@ -17625,13 +17968,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>53</v>
@@ -17654,7 +17997,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>95</v>
@@ -17708,7 +18051,7 @@
         <v>0.0</v>
       </c>
       <c r="AM17" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="AN17" s="3">
         <v>2.0</v>
@@ -17740,7 +18083,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>99</v>
@@ -17760,7 +18103,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>99</v>
@@ -17780,7 +18123,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>99</v>
@@ -17792,7 +18135,7 @@
         <v>53</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>70</v>
@@ -17800,13 +18143,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>53</v>
@@ -17829,7 +18172,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>99</v>
@@ -17883,7 +18226,7 @@
         <v>0.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="AN22" s="3">
         <v>1.0</v>
@@ -17915,7 +18258,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>49</v>
@@ -17935,7 +18278,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>49</v>
@@ -17955,7 +18298,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>49</v>
@@ -17975,13 +18318,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>69</v>
@@ -18004,7 +18347,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>49</v>
@@ -18058,7 +18401,7 @@
         <v>0.0</v>
       </c>
       <c r="AM27" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="AN27" s="3">
         <v>1.0</v>
@@ -18090,7 +18433,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>63</v>
@@ -18110,7 +18453,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>63</v>
@@ -18130,7 +18473,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>63</v>
@@ -18159,7 +18502,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>63</v>
@@ -18248,7 +18591,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>74</v>
@@ -18260,7 +18603,7 @@
         <v>51</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>55</v>
@@ -18268,7 +18611,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>74</v>
@@ -18277,7 +18620,7 @@
         <v>50</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>75</v>
@@ -18288,7 +18631,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>74</v>
@@ -18317,7 +18660,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>74</v>
@@ -18340,7 +18683,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>74</v>
@@ -18394,7 +18737,7 @@
         <v>1.0</v>
       </c>
       <c r="AM36" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="AN36" s="3">
         <v>1.0</v>
@@ -18426,7 +18769,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>80</v>
@@ -18446,7 +18789,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>80</v>
@@ -18466,7 +18809,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>80</v>
@@ -18475,7 +18818,7 @@
         <v>54</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>81</v>
@@ -18489,7 +18832,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>80</v>
@@ -18549,7 +18892,7 @@
         <v>2.0</v>
       </c>
       <c r="AM40" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="AN40" s="3">
         <v>0.0</v>
@@ -18581,7 +18924,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>85</v>
@@ -18601,7 +18944,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>85</v>
@@ -18621,13 +18964,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>53</v>
@@ -18650,7 +18993,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>85</v>
@@ -18704,7 +19047,7 @@
         <v>0.0</v>
       </c>
       <c r="AM44" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="AN44" s="3">
         <v>1.0</v>
@@ -18736,7 +19079,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>95</v>
@@ -18756,7 +19099,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>95</v>
@@ -18776,13 +19119,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>55</v>
@@ -18799,13 +19142,13 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>53</v>
@@ -18828,7 +19171,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>95</v>
@@ -18882,7 +19225,7 @@
         <v>1.0</v>
       </c>
       <c r="AM49" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AN49" s="3">
         <v>1.0</v>
@@ -18914,7 +19257,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>99</v>
@@ -18934,7 +19277,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>99</v>
@@ -18954,19 +19297,19 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>81</v>
@@ -18974,13 +19317,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>53</v>
@@ -19003,7 +19346,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>99</v>
@@ -19057,7 +19400,7 @@
         <v>1.0</v>
       </c>
       <c r="AM54" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AN54" s="3">
         <v>1.0</v>
@@ -19089,7 +19432,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>49</v>
@@ -19109,7 +19452,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>49</v>
@@ -19129,7 +19472,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>49</v>
@@ -19149,39 +19492,39 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>55</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>90</v>
@@ -19192,7 +19535,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>49</v>
@@ -19221,7 +19564,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>49</v>
@@ -19275,7 +19618,7 @@
         <v>0.0</v>
       </c>
       <c r="AM61" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="AN61" s="3">
         <v>1.0</v>
@@ -19307,7 +19650,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>63</v>
@@ -19327,7 +19670,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>63</v>
@@ -19347,7 +19690,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>63</v>
@@ -19367,7 +19710,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>63</v>
@@ -19396,7 +19739,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>63</v>
@@ -19453,7 +19796,7 @@
         <v>3.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="AN66" s="3">
         <v>1.0</v>
@@ -19485,7 +19828,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>74</v>
@@ -19505,13 +19848,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>55</v>
@@ -19525,7 +19868,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>74</v>
@@ -19545,7 +19888,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>74</v>
@@ -19574,7 +19917,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>74</v>
@@ -19603,7 +19946,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>74</v>
@@ -19663,7 +20006,7 @@
         <v>1.0</v>
       </c>
       <c r="AM72" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="AN72" s="3">
         <v>2.0</v>
@@ -19695,7 +20038,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>80</v>
@@ -19715,7 +20058,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>80</v>
@@ -19735,13 +20078,13 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>96</v>
@@ -19755,13 +20098,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>53</v>
@@ -19784,7 +20127,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>80</v>
@@ -19838,7 +20181,7 @@
         <v>0.0</v>
       </c>
       <c r="AM77" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="AN77" s="3">
         <v>1.0</v>
@@ -19870,7 +20213,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>85</v>
@@ -19890,13 +20233,13 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>96</v>
@@ -19910,7 +20253,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>85</v>
@@ -19930,7 +20273,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>85</v>
@@ -19939,7 +20282,7 @@
         <v>54</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>81</v>
@@ -19953,7 +20296,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>85</v>
@@ -20013,7 +20356,7 @@
         <v>1.0</v>
       </c>
       <c r="AM82" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AN82" s="3">
         <v>0.0</v>
@@ -20045,7 +20388,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>95</v>
@@ -20065,7 +20408,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>95</v>
@@ -20085,27 +20428,27 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>95</v>
@@ -20125,13 +20468,13 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>53</v>
@@ -20154,7 +20497,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>95</v>
@@ -20208,7 +20551,7 @@
         <v>1.0</v>
       </c>
       <c r="AM88" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AN88" s="3">
         <v>1.0</v>
@@ -20240,7 +20583,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>99</v>
@@ -20260,7 +20603,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>99</v>
@@ -20314,7 +20657,7 @@
         <v>2.0</v>
       </c>
       <c r="AM90" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AN90" s="3">
         <v>0.0</v>
@@ -20346,7 +20689,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>49</v>
@@ -20366,13 +20709,13 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>65</v>
@@ -20386,7 +20729,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>49</v>
@@ -20406,7 +20749,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>49</v>
@@ -20435,7 +20778,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>49</v>
@@ -20464,7 +20807,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>49</v>
@@ -20518,7 +20861,7 @@
         <v>1.0</v>
       </c>
       <c r="AM96" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="AN96" s="3">
         <v>2.0</v>
@@ -20550,7 +20893,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>63</v>
@@ -20570,7 +20913,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>63</v>
@@ -20590,7 +20933,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>63</v>
@@ -20602,7 +20945,7 @@
         <v>55</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>108</v>
@@ -20619,7 +20962,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>63</v>
@@ -20648,7 +20991,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>63</v>
@@ -20708,7 +21051,7 @@
         <v>1.0</v>
       </c>
       <c r="AM101" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="AN101" s="3">
         <v>2.0</v>
@@ -20740,7 +21083,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>74</v>
@@ -20760,13 +21103,13 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>55</v>
@@ -20780,7 +21123,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>74</v>
@@ -20809,7 +21152,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>74</v>
@@ -20832,7 +21175,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>74</v>
@@ -20886,7 +21229,7 @@
         <v>0.0</v>
       </c>
       <c r="AM106" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="AN106" s="3">
         <v>1.0</v>
@@ -20918,7 +21261,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>80</v>
@@ -20938,13 +21281,13 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>53</v>
@@ -20967,7 +21310,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>80</v>
@@ -21021,7 +21364,7 @@
         <v>0.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AN109" s="3">
         <v>1.0</v>
@@ -21053,7 +21396,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>85</v>
@@ -21073,7 +21416,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>85</v>
@@ -21093,7 +21436,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>85</v>
@@ -21113,13 +21456,13 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>55</v>
@@ -21133,13 +21476,13 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I114" s="2" t="s">
         <v>53</v>
@@ -21162,7 +21505,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>85</v>
@@ -21225,7 +21568,7 @@
         <v>1.0</v>
       </c>
       <c r="AM115" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="AN115" s="3">
         <v>1.0</v>
@@ -21257,13 +21600,13 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>55</v>
@@ -21277,7 +21620,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>95</v>
@@ -21297,7 +21640,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>95</v>
@@ -21317,7 +21660,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>95</v>
@@ -21329,21 +21672,21 @@
         <v>56</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I120" s="2" t="s">
         <v>55</v>
@@ -21366,13 +21709,13 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>53</v>
@@ -21395,7 +21738,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>95</v>
@@ -21449,7 +21792,7 @@
         <v>0.0</v>
       </c>
       <c r="AM122" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AN122" s="3">
         <v>2.0</v>
@@ -21481,7 +21824,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>99</v>
@@ -21501,13 +21844,13 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>55</v>
@@ -21521,7 +21864,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>99</v>
@@ -21541,7 +21884,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>99</v>
@@ -21570,7 +21913,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>99</v>
@@ -21624,7 +21967,7 @@
         <v>1.0</v>
       </c>
       <c r="AM127" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="AN127" s="3">
         <v>1.0</v>
@@ -21656,7 +21999,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>49</v>
@@ -21676,7 +22019,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>49</v>
@@ -21696,13 +22039,13 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I130" s="2" t="s">
         <v>55</v>
@@ -21719,7 +22062,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>49</v>
@@ -21779,7 +22122,7 @@
         <v>0.0</v>
       </c>
       <c r="AM131" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AN131" s="3">
         <v>0.0</v>
@@ -21811,7 +22154,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>63</v>
@@ -21831,13 +22174,13 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>96</v>
@@ -21846,12 +22189,12 @@
         <v>53</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>63</v>
@@ -21871,7 +22214,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>63</v>
@@ -21891,7 +22234,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>63</v>
@@ -21920,13 +22263,13 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I137" s="2" t="s">
         <v>69</v>
@@ -21949,7 +22292,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>63</v>
@@ -22009,7 +22352,7 @@
         <v>0.0</v>
       </c>
       <c r="AM138" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="AN138" s="3">
         <v>2.0</v>
@@ -22199,7 +22542,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>99</v>
@@ -22219,7 +22562,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>99</v>
@@ -22239,7 +22582,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>99</v>
@@ -22262,7 +22605,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>99</v>
@@ -22291,7 +22634,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>99</v>
@@ -22300,7 +22643,7 @@
         <v>92</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>81</v>
@@ -22320,7 +22663,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>99</v>
@@ -22374,7 +22717,7 @@
         <v>0.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="AN7" s="3">
         <v>2.0</v>
@@ -22406,7 +22749,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>49</v>
@@ -22426,7 +22769,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>49</v>
@@ -22446,7 +22789,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>49</v>
@@ -22475,7 +22818,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -22504,7 +22847,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>49</v>
@@ -22558,7 +22901,7 @@
         <v>0.0</v>
       </c>
       <c r="AM12" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AN12" s="3">
         <v>2.0</v>
@@ -22590,7 +22933,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>63</v>
@@ -22610,7 +22953,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>63</v>
@@ -22630,13 +22973,13 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>55</v>
@@ -22662,7 +23005,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>63</v>
@@ -22716,7 +23059,7 @@
         <v>1.0</v>
       </c>
       <c r="AM16" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="AN16" s="3">
         <v>1.0</v>
@@ -22748,7 +23091,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>74</v>
@@ -22768,7 +23111,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>74</v>
@@ -22788,7 +23131,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>74</v>
@@ -22804,7 +23147,7 @@
         <v>55</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>121</v>
@@ -22815,7 +23158,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>74</v>
@@ -22848,7 +23191,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>74</v>
@@ -22909,7 +23252,7 @@
         <v>0.0</v>
       </c>
       <c r="AM21" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AN21" s="3">
         <v>1.0</v>
@@ -22941,7 +23284,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>80</v>
@@ -22961,7 +23304,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>80</v>
@@ -22981,13 +23324,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>55</v>
@@ -23010,7 +23353,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>80</v>
@@ -23070,7 +23413,7 @@
         <v>0.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="AN25" s="3">
         <v>1.0</v>
@@ -23102,7 +23445,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>85</v>
@@ -23122,7 +23465,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>85</v>
@@ -23142,13 +23485,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>53</v>
@@ -23171,7 +23514,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>85</v>
@@ -23194,7 +23537,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>85</v>
@@ -23254,7 +23597,7 @@
         <v>0.0</v>
       </c>
       <c r="AM30" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="AN30" s="3">
         <v>1.0</v>
@@ -23286,7 +23629,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>95</v>
@@ -23306,7 +23649,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>95</v>
@@ -23326,7 +23669,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>95</v>
@@ -23336,7 +23679,7 @@
       <c r="E33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>55</v>
@@ -23353,7 +23696,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>95</v>
@@ -23363,7 +23706,7 @@
       <c r="E34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>53</v>
@@ -23380,7 +23723,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>95</v>
@@ -23393,7 +23736,7 @@
         <v>0.0</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>106</v>
@@ -23444,7 +23787,7 @@
         <v>0.0</v>
       </c>
       <c r="AM35" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AN35" s="3">
         <v>0.0</v>
@@ -23476,7 +23819,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>99</v>
@@ -23496,7 +23839,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>99</v>
@@ -23516,13 +23859,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>59</v>
@@ -23545,7 +23888,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>99</v>
@@ -23605,7 +23948,7 @@
         <v>0.0</v>
       </c>
       <c r="AM39" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AN39" s="3">
         <v>1.0</v>
@@ -23637,7 +23980,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>49</v>
@@ -23657,13 +24000,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>55</v>
@@ -23680,13 +24023,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>53</v>
@@ -23709,7 +24052,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>49</v>
@@ -23763,7 +24106,7 @@
         <v>3.0</v>
       </c>
       <c r="AM43" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="AN43" s="3">
         <v>1.0</v>
@@ -23795,7 +24138,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>63</v>
@@ -23815,7 +24158,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>63</v>
@@ -23835,13 +24178,13 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>55</v>
@@ -23864,13 +24207,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>53</v>
@@ -23893,7 +24236,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>63</v>
@@ -23979,7 +24322,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>74</v>
@@ -23999,7 +24342,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>74</v>
@@ -24031,7 +24374,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>74</v>
@@ -24094,7 +24437,7 @@
         <v>0.0</v>
       </c>
       <c r="AM51" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AN51" s="3">
         <v>1.0</v>
@@ -24126,7 +24469,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>80</v>
@@ -24146,7 +24489,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>80</v>
@@ -24166,13 +24509,13 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>53</v>
@@ -24195,7 +24538,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>80</v>
@@ -24249,7 +24592,7 @@
         <v>2.0</v>
       </c>
       <c r="AM55" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="AN55" s="3">
         <v>1.0</v>
@@ -24281,7 +24624,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>85</v>
@@ -24301,7 +24644,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>85</v>
@@ -24321,13 +24664,13 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>53</v>
@@ -24350,7 +24693,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>85</v>
@@ -24404,7 +24747,7 @@
         <v>0.0</v>
       </c>
       <c r="AM59" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AN59" s="3">
         <v>1.0</v>
@@ -24436,7 +24779,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>95</v>
@@ -24456,7 +24799,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>95</v>
@@ -24476,7 +24819,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>95</v>
@@ -24530,7 +24873,7 @@
         <v>0.0</v>
       </c>
       <c r="AM62" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="AN62" s="3">
         <v>0.0</v>
@@ -24562,7 +24905,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>99</v>
@@ -24582,7 +24925,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>99</v>
@@ -24602,16 +24945,16 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>81</v>
@@ -24634,7 +24977,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>99</v>
@@ -24688,7 +25031,7 @@
         <v>0.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="AN66" s="3">
         <v>1.0</v>
@@ -24720,7 +25063,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>49</v>
@@ -24740,7 +25083,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>49</v>
@@ -24760,13 +25103,13 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>53</v>
@@ -24789,7 +25132,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>49</v>
@@ -24843,7 +25186,7 @@
         <v>0.0</v>
       </c>
       <c r="AM70" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="AN70" s="3">
         <v>1.0</v>
@@ -24875,7 +25218,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>63</v>
@@ -24895,7 +25238,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>63</v>
@@ -24915,7 +25258,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>63</v>
@@ -24944,7 +25287,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>63</v>
@@ -24998,7 +25341,7 @@
         <v>0.0</v>
       </c>
       <c r="AM74" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="AN74" s="3">
         <v>1.0</v>
@@ -25030,7 +25373,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>74</v>
@@ -25050,7 +25393,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>74</v>
@@ -25070,13 +25413,13 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>74</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>55</v>
@@ -25099,7 +25442,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>74</v>
@@ -25122,7 +25465,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>74</v>
@@ -25176,7 +25519,7 @@
         <v>1.0</v>
       </c>
       <c r="AM79" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="AN79" s="3">
         <v>1.0</v>
@@ -25208,7 +25551,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>80</v>
@@ -25228,13 +25571,13 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>56</v>
@@ -25257,7 +25600,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>80</v>
@@ -25317,7 +25660,7 @@
         <v>0.0</v>
       </c>
       <c r="AM82" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="AN82" s="3">
         <v>1.0</v>
@@ -25349,7 +25692,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>85</v>
@@ -25369,7 +25712,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>85</v>
@@ -25389,7 +25732,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>85</v>
@@ -25418,13 +25761,13 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>56</v>
@@ -25447,7 +25790,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>85</v>
@@ -25507,7 +25850,7 @@
         <v>0.0</v>
       </c>
       <c r="AM87" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AN87" s="3">
         <v>2.0</v>
@@ -25539,7 +25882,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>95</v>
@@ -25559,7 +25902,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>95</v>
@@ -25579,7 +25922,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>95</v>
@@ -25608,7 +25951,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>95</v>
@@ -25662,7 +26005,7 @@
         <v>1.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="AN91" s="3">
         <v>1.0</v>
@@ -25694,7 +26037,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>99</v>
@@ -25714,7 +26057,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>99</v>
@@ -25734,7 +26077,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>99</v>
@@ -25763,7 +26106,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>99</v>
@@ -25817,7 +26160,7 @@
         <v>0.0</v>
       </c>
       <c r="AM95" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="AN95" s="3">
         <v>1.0</v>
@@ -25849,7 +26192,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>49</v>
@@ -25869,7 +26212,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>49</v>
@@ -25889,13 +26232,13 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>55</v>
@@ -25918,7 +26261,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>49</v>
@@ -25947,7 +26290,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>49</v>
@@ -26001,7 +26344,7 @@
         <v>0.0</v>
       </c>
       <c r="AM100" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="AN100" s="3">
         <v>2.0</v>
@@ -26033,7 +26376,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>63</v>
@@ -26053,7 +26396,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>63</v>
@@ -26073,7 +26416,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>63</v>
@@ -26102,7 +26445,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>63</v>
@@ -26156,7 +26499,7 @@
         <v>2.0</v>
       </c>
       <c r="AM104" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="AN104" s="3">
         <v>1.0</v>
@@ -26188,7 +26531,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>74</v>
@@ -26208,7 +26551,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>74</v>
@@ -26228,7 +26571,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>74</v>
@@ -26240,7 +26583,7 @@
         <v>96</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="L107" s="2" t="s">
         <v>52</v>
@@ -26257,7 +26600,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>74</v>
@@ -26286,7 +26629,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>74</v>
@@ -26346,7 +26689,7 @@
         <v>2.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AN109" s="3">
         <v>2.0</v>
@@ -26378,7 +26721,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>80</v>
@@ -26398,7 +26741,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>80</v>
@@ -26418,7 +26761,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>80</v>
@@ -26441,7 +26784,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>80</v>
@@ -26470,7 +26813,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>80</v>
@@ -26524,7 +26867,7 @@
         <v>0.0</v>
       </c>
       <c r="AM114" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="AN114" s="3">
         <v>1.0</v>
@@ -26556,7 +26899,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>85</v>
@@ -26576,7 +26919,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>85</v>
@@ -26596,7 +26939,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>85</v>
@@ -26616,7 +26959,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>85</v>
@@ -26645,7 +26988,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>85</v>
@@ -26702,7 +27045,7 @@
         <v>0.0</v>
       </c>
       <c r="AM119" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AN119" s="3">
         <v>1.0</v>
@@ -26734,7 +27077,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>95</v>
@@ -26754,7 +27097,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>95</v>
@@ -26774,7 +27117,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>95</v>
@@ -26803,7 +27146,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>95</v>
@@ -26826,7 +27169,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>95</v>
@@ -26883,7 +27226,7 @@
         <v>1.0</v>
       </c>
       <c r="AM124" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AN124" s="3">
         <v>1.0</v>
@@ -26915,7 +27258,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>99</v>
@@ -26935,7 +27278,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>99</v>
@@ -26955,7 +27298,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>99</v>
@@ -26975,7 +27318,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>99</v>
@@ -27004,7 +27347,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>99</v>
@@ -27064,7 +27407,7 @@
         <v>1.0</v>
       </c>
       <c r="AM129" s="1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AN129" s="3">
         <v>1.0</v>
@@ -27096,7 +27439,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>49</v>
@@ -27116,7 +27459,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>49</v>
@@ -27136,7 +27479,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>49</v>
@@ -27156,13 +27499,13 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I133" s="2" t="s">
         <v>55</v>
@@ -27185,13 +27528,13 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I134" s="2" t="s">
         <v>53</v>
@@ -27214,7 +27557,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>49</v>
@@ -27268,7 +27611,7 @@
         <v>0.0</v>
       </c>
       <c r="AM135" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AN135" s="3">
         <v>2.0</v>
@@ -27300,7 +27643,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>63</v>
@@ -27320,7 +27663,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>63</v>
@@ -27340,7 +27683,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>63</v>
@@ -27360,7 +27703,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>63</v>
@@ -27389,13 +27732,13 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I140" s="2" t="s">
         <v>53</v>
@@ -27418,7 +27761,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>63</v>
@@ -27472,7 +27815,7 @@
         <v>0.0</v>
       </c>
       <c r="AM141" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AN141" s="3">
         <v>2.0</v>

--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Bolevec/Databaze Bolevec 2026.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Bolevec/Databaze Bolevec 2026.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4153" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4375" uniqueCount="394">
   <si>
     <t>Datum</t>
   </si>
@@ -429,6 +429,66 @@
     <t>7 min 07 s</t>
   </si>
   <si>
+    <t>22.05.2026</t>
+  </si>
+  <si>
+    <t>12 min 12 s</t>
+  </si>
+  <si>
+    <t>23.05.2026</t>
+  </si>
+  <si>
+    <t>11 min 35 s</t>
+  </si>
+  <si>
+    <t>24.05.2026</t>
+  </si>
+  <si>
+    <t>03:30</t>
+  </si>
+  <si>
+    <t>10 min 16 s</t>
+  </si>
+  <si>
+    <t>25.05.2026</t>
+  </si>
+  <si>
+    <t>12 min 28 s</t>
+  </si>
+  <si>
+    <t>26.05.2026</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>11 min 28 s</t>
+  </si>
+  <si>
+    <t>27.05.2026</t>
+  </si>
+  <si>
+    <t>11 min 53 s</t>
+  </si>
+  <si>
+    <t>28.05.2026</t>
+  </si>
+  <si>
+    <t>16 min 22 s</t>
+  </si>
+  <si>
+    <t>29.05.2026</t>
+  </si>
+  <si>
+    <t>16 min 49 s</t>
+  </si>
+  <si>
+    <t>30.05.2026</t>
+  </si>
+  <si>
+    <t>12 min 40 s</t>
+  </si>
+  <si>
     <t>01.04.2026</t>
   </si>
   <si>
@@ -510,18 +570,12 @@
     <t>18:30</t>
   </si>
   <si>
-    <t>15:30</t>
-  </si>
-  <si>
     <t>11.04.2026</t>
   </si>
   <si>
     <t>19:30</t>
   </si>
   <si>
-    <t>03:30</t>
-  </si>
-  <si>
     <t>14 min 27 s</t>
   </si>
   <si>
@@ -549,9 +603,6 @@
     <t>15.04.2026</t>
   </si>
   <si>
-    <t>12 min 12 s</t>
-  </si>
-  <si>
     <t>16.04.2026</t>
   </si>
   <si>
@@ -685,9 +736,6 @@
   </si>
   <si>
     <t>05:30</t>
-  </si>
-  <si>
-    <t>11 min 28 s</t>
   </si>
   <si>
     <t>07.03.2026</t>
@@ -5315,6 +5363,1553 @@
         <v>0.0</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M97" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N97" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O97" s="3">
+        <v>45.0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M98" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="N98" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O98" s="3">
+        <v>360.0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>6903.84</v>
+      </c>
+      <c r="T99" s="3">
+        <v>2029.0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>2034.0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>1334.0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>778.0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>3839.0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>3451.0</v>
+      </c>
+      <c r="AB99" s="3">
+        <v>19995.839999999997</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>3.637978807091713E-12</v>
+      </c>
+      <c r="AD99" s="3">
+        <v>0.34171602144859037</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>405.0</v>
+      </c>
+      <c r="AJ99" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>284.0</v>
+      </c>
+      <c r="AL99" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM99" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AN99" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AO99" s="3">
+        <v>61.0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="AR99" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS99" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT99" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU99" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV99" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M102" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N102" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O102" s="3">
+        <v>315.0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P103" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q103" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R103" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S103" s="3">
+        <v>6511.590000000001</v>
+      </c>
+      <c r="T103" s="3">
+        <v>3613.0</v>
+      </c>
+      <c r="U103" s="3">
+        <v>2265.75</v>
+      </c>
+      <c r="V103" s="3">
+        <v>2867.0</v>
+      </c>
+      <c r="W103" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X103" s="3">
+        <v>408.0</v>
+      </c>
+      <c r="Y103" s="3">
+        <v>2497.0</v>
+      </c>
+      <c r="AA103" s="3">
+        <v>2164.0</v>
+      </c>
+      <c r="AB103" s="3">
+        <v>20232.839999999997</v>
+      </c>
+      <c r="AC103" s="3">
+        <v>0.500000000003638</v>
+      </c>
+      <c r="AD103" s="3">
+        <v>0.44142744618761287</v>
+      </c>
+      <c r="AI103" s="3">
+        <v>315.0</v>
+      </c>
+      <c r="AJ103" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK103" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL103" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AM103" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AN103" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO103" s="3">
+        <v>52.0</v>
+      </c>
+      <c r="AP103" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="AQ103" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AR103" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AS103" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT103" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU103" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV103" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="M106" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N106" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O106" s="3">
+        <v>315.0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="N107" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P108" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="S108" s="3">
+        <v>10726.31</v>
+      </c>
+      <c r="T108" s="3">
+        <v>319.0</v>
+      </c>
+      <c r="U108" s="3">
+        <v>3452.5</v>
+      </c>
+      <c r="V108" s="3">
+        <v>1818.0</v>
+      </c>
+      <c r="W108" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X108" s="3">
+        <v>1492.75</v>
+      </c>
+      <c r="Y108" s="3">
+        <v>1199.0</v>
+      </c>
+      <c r="AA108" s="3">
+        <v>2580.0</v>
+      </c>
+      <c r="AB108" s="3">
+        <v>20508.759999999995</v>
+      </c>
+      <c r="AC108" s="3">
+        <v>0.05000000000291038</v>
+      </c>
+      <c r="AD108" s="3">
+        <v>0.4474199556834534</v>
+      </c>
+      <c r="AH108" s="3">
+        <v>99.0</v>
+      </c>
+      <c r="AI108" s="3">
+        <v>315.0</v>
+      </c>
+      <c r="AJ108" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK108" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL108" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM108" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AN108" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO108" s="3">
+        <v>58.0</v>
+      </c>
+      <c r="AP108" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="AQ108" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="AR108" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS108" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT108" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU108" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV108" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L111" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M111" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="N111" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O111" s="3">
+        <v>270.0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="P112" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q112" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R112" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S112" s="3">
+        <v>3101.8899999999994</v>
+      </c>
+      <c r="T112" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="U112" s="3">
+        <v>2125.25</v>
+      </c>
+      <c r="V112" s="3">
+        <v>1296.0</v>
+      </c>
+      <c r="W112" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X112" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y112" s="3">
+        <v>4117.0</v>
+      </c>
+      <c r="AA112" s="3">
+        <v>1400.0</v>
+      </c>
+      <c r="AB112" s="3">
+        <v>12306.74</v>
+      </c>
+      <c r="AC112" s="3">
+        <v>3.399999999999636</v>
+      </c>
+      <c r="AD112" s="3">
+        <v>0.641472468770981</v>
+      </c>
+      <c r="AI112" s="3">
+        <v>270.0</v>
+      </c>
+      <c r="AJ112" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK112" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL112" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM112" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="AN112" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO112" s="3">
+        <v>46.0</v>
+      </c>
+      <c r="AP112" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AQ112" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AR112" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS112" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT112" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU112" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV112" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L115" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="M115" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N115" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O115" s="3">
+        <v>315.0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="P116" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q116" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R116" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S116" s="3">
+        <v>6271.78</v>
+      </c>
+      <c r="T116" s="3">
+        <v>638.0</v>
+      </c>
+      <c r="U116" s="3">
+        <v>3508.0</v>
+      </c>
+      <c r="V116" s="3">
+        <v>1032.0</v>
+      </c>
+      <c r="W116" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X116" s="3">
+        <v>496.0</v>
+      </c>
+      <c r="Y116" s="3">
+        <v>2603.0</v>
+      </c>
+      <c r="AA116" s="3">
+        <v>3376.0</v>
+      </c>
+      <c r="AB116" s="3">
+        <v>17743.58</v>
+      </c>
+      <c r="AC116" s="3">
+        <v>0.19999999999708962</v>
+      </c>
+      <c r="AD116" s="3">
+        <v>0.4737131790947813</v>
+      </c>
+      <c r="AI116" s="3">
+        <v>315.0</v>
+      </c>
+      <c r="AJ116" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK116" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL116" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM116" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="AN116" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO116" s="3">
+        <v>56.0</v>
+      </c>
+      <c r="AP116" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="AQ116" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AR116" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS116" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT116" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU116" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV116" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J119" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L119" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M119" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N119" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O119" s="3">
+        <v>180.0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="P120" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="S120" s="3">
+        <v>3825.2200000000003</v>
+      </c>
+      <c r="T120" s="3">
+        <v>632.0</v>
+      </c>
+      <c r="U120" s="3">
+        <v>2681.5</v>
+      </c>
+      <c r="V120" s="3">
+        <v>217.0</v>
+      </c>
+      <c r="W120" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X120" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y120" s="3">
+        <v>3012.0</v>
+      </c>
+      <c r="AA120" s="3">
+        <v>1163.0</v>
+      </c>
+      <c r="AB120" s="3">
+        <v>11710.72</v>
+      </c>
+      <c r="AC120" s="3">
+        <v>1.8189894035458565E-12</v>
+      </c>
+      <c r="AD120" s="3">
+        <v>0.6387339882024831</v>
+      </c>
+      <c r="AI120" s="3">
+        <v>180.0</v>
+      </c>
+      <c r="AJ120" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK120" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL120" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM120" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="AN120" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO120" s="3">
+        <v>39.0</v>
+      </c>
+      <c r="AP120" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="AQ120" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="AR120" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS120" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT120" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU120" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV120" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J123" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L123" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M123" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N123" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O123" s="3">
+        <v>45.0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J124" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L124" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M124" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N124" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O124" s="3">
+        <v>180.0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="P125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="S125" s="3">
+        <v>5401.24</v>
+      </c>
+      <c r="T125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="U125" s="3">
+        <v>3362.75</v>
+      </c>
+      <c r="V125" s="3">
+        <v>1530.4</v>
+      </c>
+      <c r="W125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y125" s="3">
+        <v>2929.0</v>
+      </c>
+      <c r="AA125" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AB125" s="3">
+        <v>14337.189999999999</v>
+      </c>
+      <c r="AC125" s="3">
+        <v>7.200000000000728</v>
+      </c>
+      <c r="AD125" s="3">
+        <v>0.6149616549911511</v>
+      </c>
+      <c r="AH125" s="3">
+        <v>796.0</v>
+      </c>
+      <c r="AI125" s="3">
+        <v>225.0</v>
+      </c>
+      <c r="AJ125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM125" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="AN125" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AO125" s="3">
+        <v>44.0</v>
+      </c>
+      <c r="AP125" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="AQ125" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AR125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU125" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV125" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J128" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L128" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M128" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N128" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O128" s="3">
+        <v>135.0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J129" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L129" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M129" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N129" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O129" s="3">
+        <v>315.0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P130" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q130" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R130" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S130" s="3">
+        <v>5596.319999999999</v>
+      </c>
+      <c r="T130" s="3">
+        <v>3587.0</v>
+      </c>
+      <c r="U130" s="3">
+        <v>2649.0</v>
+      </c>
+      <c r="V130" s="3">
+        <v>2223.0</v>
+      </c>
+      <c r="W130" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X130" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y130" s="3">
+        <v>3276.0</v>
+      </c>
+      <c r="AA130" s="3">
+        <v>1740.0</v>
+      </c>
+      <c r="AB130" s="3">
+        <v>19519.519999999997</v>
+      </c>
+      <c r="AC130" s="3">
+        <v>1.8000000000029104</v>
+      </c>
+      <c r="AD130" s="3">
+        <v>0.5390065170825195</v>
+      </c>
+      <c r="AI130" s="3">
+        <v>450.0</v>
+      </c>
+      <c r="AJ130" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AK130" s="3">
+        <v>207.0</v>
+      </c>
+      <c r="AL130" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM130" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="AN130" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AO130" s="3">
+        <v>58.0</v>
+      </c>
+      <c r="AP130" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="AQ130" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="AR130" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS130" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT130" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU130" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV130" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L133" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M133" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N133" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O133" s="3">
+        <v>135.0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J134" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L134" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M134" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="N134" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O134" s="3">
+        <v>405.0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P135" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="S135" s="3">
+        <v>8698.659999999998</v>
+      </c>
+      <c r="T135" s="3">
+        <v>2715.0</v>
+      </c>
+      <c r="U135" s="3">
+        <v>5332.75</v>
+      </c>
+      <c r="V135" s="3">
+        <v>2113.0</v>
+      </c>
+      <c r="W135" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X135" s="3">
+        <v>1295.0</v>
+      </c>
+      <c r="Y135" s="3">
+        <v>2465.0</v>
+      </c>
+      <c r="AA135" s="3">
+        <v>2556.0</v>
+      </c>
+      <c r="AB135" s="3">
+        <v>24420.209999999992</v>
+      </c>
+      <c r="AC135" s="3">
+        <v>0.20000000000436557</v>
+      </c>
+      <c r="AD135" s="3">
+        <v>0.3919196964449767</v>
+      </c>
+      <c r="AI135" s="3">
+        <v>540.0</v>
+      </c>
+      <c r="AJ135" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AK135" s="3">
+        <v>518.0</v>
+      </c>
+      <c r="AL135" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="AM135" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN135" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AO135" s="3">
+        <v>57.0</v>
+      </c>
+      <c r="AP135" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="AQ135" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="AR135" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="AS135" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="AT135" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU135" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="AV135" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -5475,7 +7070,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>95</v>
@@ -5495,7 +7090,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>95</v>
@@ -5515,13 +7110,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>55</v>
@@ -5535,7 +7130,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>95</v>
@@ -5547,10 +7142,10 @@
         <v>55</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="M5" s="3">
         <v>5.0</v>
@@ -5564,7 +7159,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>95</v>
@@ -5624,7 +7219,7 @@
         <v>0.0</v>
       </c>
       <c r="AM6" s="1" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="AN6" s="3">
         <v>1.0</v>
@@ -5656,7 +7251,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>99</v>
@@ -5676,13 +7271,13 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>53</v>
@@ -5696,7 +7291,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>99</v>
@@ -5725,7 +7320,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>99</v>
@@ -5754,7 +7349,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>99</v>
@@ -5814,7 +7409,7 @@
         <v>0.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="AN11" s="3">
         <v>2.0</v>
@@ -5846,7 +7441,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>49</v>
@@ -5858,7 +7453,7 @@
         <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>67</v>
@@ -5866,13 +7461,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>55</v>
@@ -5886,7 +7481,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>49</v>
@@ -5906,7 +7501,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>49</v>
@@ -5935,7 +7530,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>49</v>
@@ -5964,7 +7559,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>49</v>
@@ -6027,7 +7622,7 @@
         <v>0.0</v>
       </c>
       <c r="AM17" s="1" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="AN17" s="3">
         <v>2.0</v>
@@ -6059,7 +7654,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>63</v>
@@ -6079,13 +7674,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>55</v>
@@ -6099,7 +7694,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>63</v>
@@ -6119,7 +7714,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>63</v>
@@ -6139,7 +7734,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>63</v>
@@ -6168,7 +7763,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>63</v>
@@ -6197,7 +7792,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>63</v>
@@ -6257,7 +7852,7 @@
         <v>0.0</v>
       </c>
       <c r="AM24" s="1" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="AN24" s="3">
         <v>2.0</v>
@@ -6289,7 +7884,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>74</v>
@@ -6309,7 +7904,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>74</v>
@@ -6341,7 +7936,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>74</v>
@@ -6401,7 +7996,7 @@
         <v>0.0</v>
       </c>
       <c r="AM27" s="1" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="AN27" s="3">
         <v>1.0</v>
@@ -6433,7 +8028,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>80</v>
@@ -6453,13 +8048,13 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>55</v>
@@ -6473,7 +8068,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>80</v>
@@ -6493,7 +8088,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>80</v>
@@ -6526,7 +8121,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>80</v>
@@ -6539,7 +8134,7 @@
         <v>92</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>81</v>
@@ -6553,7 +8148,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>80</v>
@@ -6569,7 +8164,7 @@
         <v>53</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>107</v>
@@ -6586,7 +8181,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>80</v>
@@ -6650,7 +8245,7 @@
         <v>0.0</v>
       </c>
       <c r="AM34" s="1" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="AN34" s="3">
         <v>2.0</v>
@@ -6682,7 +8277,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>85</v>
@@ -6694,7 +8289,7 @@
         <v>51</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>114</v>
@@ -6702,7 +8297,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>85</v>
@@ -6722,7 +8317,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>85</v>
@@ -6742,7 +8337,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>85</v>
@@ -6765,7 +8360,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>85</v>
@@ -6794,7 +8389,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>85</v>
@@ -6854,7 +8449,7 @@
         <v>0.0</v>
       </c>
       <c r="AM40" s="1" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="AN40" s="3">
         <v>1.0</v>
@@ -6886,7 +8481,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>95</v>
@@ -6906,13 +8501,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>55</v>
@@ -6926,7 +8521,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>95</v>
@@ -6946,7 +8541,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>95</v>
@@ -6955,7 +8550,7 @@
         <v>92</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>81</v>
@@ -6969,7 +8564,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>95</v>
@@ -7026,7 +8621,7 @@
         <v>0.0</v>
       </c>
       <c r="AM45" s="1" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="AN45" s="3">
         <v>0.0</v>
@@ -7058,7 +8653,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>99</v>
@@ -7078,13 +8673,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>55</v>
@@ -7098,7 +8693,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>99</v>
@@ -7127,7 +8722,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>99</v>
@@ -7187,7 +8782,7 @@
         <v>0.0</v>
       </c>
       <c r="AM49" s="1" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="AN49" s="3">
         <v>1.0</v>
@@ -7219,7 +8814,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>49</v>
@@ -7231,7 +8826,7 @@
         <v>51</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>108</v>
@@ -7239,16 +8834,16 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>86</v>
@@ -7259,7 +8854,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>49</v>
@@ -7279,7 +8874,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>49</v>
@@ -7291,7 +8886,7 @@
         <v>55</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>90</v>
@@ -7308,7 +8903,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>49</v>
@@ -7317,7 +8912,7 @@
         <v>58</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>52</v>
@@ -7337,7 +8932,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>49</v>
@@ -7429,7 +9024,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>63</v>
@@ -7449,19 +9044,19 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>108</v>
@@ -7469,7 +9064,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>63</v>
@@ -7481,7 +9076,7 @@
         <v>53</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>65</v>
@@ -7489,7 +9084,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>63</v>
@@ -7512,7 +9107,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>63</v>
@@ -7541,7 +9136,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>63</v>
@@ -7604,7 +9199,7 @@
         <v>3.0</v>
       </c>
       <c r="AM61" s="1" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="AN61" s="3">
         <v>1.0</v>
@@ -7636,7 +9231,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>74</v>
@@ -7656,13 +9251,13 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>55</v>
@@ -7676,7 +9271,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>74</v>
@@ -7696,7 +9291,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>74</v>
@@ -7725,7 +9320,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>74</v>
@@ -7754,7 +9349,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>74</v>
@@ -7814,7 +9409,7 @@
         <v>0.0</v>
       </c>
       <c r="AM67" s="1" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="AN67" s="3">
         <v>2.0</v>
@@ -7846,7 +9441,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>80</v>
@@ -7858,7 +9453,7 @@
         <v>51</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>114</v>
@@ -7866,13 +9461,13 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>87</v>
@@ -7886,7 +9481,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>80</v>
@@ -7906,7 +9501,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>80</v>
@@ -7935,7 +9530,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>80</v>
@@ -7998,7 +9593,7 @@
         <v>0.0</v>
       </c>
       <c r="AM72" s="1" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="AN72" s="3">
         <v>1.0</v>
@@ -8030,7 +9625,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>85</v>
@@ -8050,13 +9645,13 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>55</v>
@@ -8070,7 +9665,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>85</v>
@@ -8090,7 +9685,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>85</v>
@@ -8108,7 +9703,7 @@
         <v>121</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="M76" s="3">
         <v>2.0</v>
@@ -8122,7 +9717,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>85</v>
@@ -8182,7 +9777,7 @@
         <v>0.0</v>
       </c>
       <c r="AM77" s="1" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="AN77" s="3">
         <v>1.0</v>
@@ -8214,7 +9809,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>95</v>
@@ -8234,7 +9829,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>95</v>
@@ -8254,7 +9849,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>95</v>
@@ -8277,7 +9872,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>95</v>
@@ -8306,7 +9901,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>95</v>
@@ -8366,7 +9961,7 @@
         <v>0.0</v>
       </c>
       <c r="AM82" s="1" t="s">
-        <v>177</v>
+        <v>138</v>
       </c>
       <c r="AN82" s="3">
         <v>1.0</v>
@@ -8398,7 +9993,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>99</v>
@@ -8418,7 +10013,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>99</v>
@@ -8438,7 +10033,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>99</v>
@@ -8450,7 +10045,7 @@
         <v>59</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>67</v>
@@ -8467,7 +10062,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>99</v>
@@ -8530,7 +10125,7 @@
         <v>0.0</v>
       </c>
       <c r="AM86" s="1" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="AN86" s="3">
         <v>1.0</v>
@@ -8562,7 +10157,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>49</v>
@@ -8574,7 +10169,7 @@
         <v>51</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>67</v>
@@ -8582,7 +10177,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>49</v>
@@ -8602,7 +10197,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>49</v>
@@ -8631,7 +10226,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>49</v>
@@ -8660,7 +10255,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>49</v>
@@ -8720,7 +10315,7 @@
         <v>0.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="AN91" s="3">
         <v>2.0</v>
@@ -8752,7 +10347,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>63</v>
@@ -8772,7 +10367,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>63</v>
@@ -8801,7 +10396,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>63</v>
@@ -8830,7 +10425,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>63</v>
@@ -8884,7 +10479,7 @@
         <v>0.0</v>
       </c>
       <c r="AM95" s="1" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="AN95" s="3">
         <v>2.0</v>
@@ -8916,7 +10511,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>74</v>
@@ -8936,7 +10531,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>74</v>
@@ -8965,7 +10560,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>74</v>
@@ -9019,7 +10614,7 @@
         <v>1.0</v>
       </c>
       <c r="AM98" s="1" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="AN98" s="3">
         <v>1.0</v>
@@ -9051,7 +10646,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>80</v>
@@ -9071,7 +10666,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>80</v>
@@ -9091,7 +10686,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>80</v>
@@ -9120,7 +10715,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>80</v>
@@ -9174,7 +10769,7 @@
         <v>1.0</v>
       </c>
       <c r="AM102" s="1" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="AN102" s="3">
         <v>1.0</v>
@@ -9206,7 +10801,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>85</v>
@@ -9226,7 +10821,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>85</v>
@@ -9246,7 +10841,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>85</v>
@@ -9275,7 +10870,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>85</v>
@@ -9287,7 +10882,7 @@
         <v>59</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="L106" s="2" t="s">
         <v>67</v>
@@ -9304,7 +10899,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>85</v>
@@ -9364,7 +10959,7 @@
         <v>0.0</v>
       </c>
       <c r="AM107" s="1" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="AN107" s="3">
         <v>2.0</v>
@@ -9396,7 +10991,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>95</v>
@@ -9416,7 +11011,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>95</v>
@@ -9436,7 +11031,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>95</v>
@@ -9468,7 +11063,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>95</v>
@@ -9531,7 +11126,7 @@
         <v>0.0</v>
       </c>
       <c r="AM111" s="1" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="AN111" s="3">
         <v>1.0</v>
@@ -9563,7 +11158,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>99</v>
@@ -9583,7 +11178,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>99</v>
@@ -9603,7 +11198,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>99</v>
@@ -9632,7 +11227,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>99</v>
@@ -9695,7 +11290,7 @@
         <v>2.0</v>
       </c>
       <c r="AM115" s="1" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="AN115" s="3">
         <v>1.0</v>
@@ -9727,7 +11322,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>49</v>
@@ -9747,7 +11342,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>49</v>
@@ -9770,7 +11365,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>49</v>
@@ -9790,7 +11385,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>49</v>
@@ -9819,7 +11414,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>49</v>
@@ -9848,7 +11443,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>49</v>
@@ -9908,7 +11503,7 @@
         <v>2.0</v>
       </c>
       <c r="AM121" s="1" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="AN121" s="3">
         <v>2.0</v>
@@ -9940,7 +11535,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>63</v>
@@ -9952,7 +11547,7 @@
         <v>51</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>108</v>
@@ -9960,7 +11555,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>63</v>
@@ -9980,7 +11575,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>63</v>
@@ -10009,7 +11604,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>63</v>
@@ -10038,7 +11633,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>63</v>
@@ -10101,7 +11696,7 @@
         <v>1.0</v>
       </c>
       <c r="AM126" s="1" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="AN126" s="3">
         <v>2.0</v>
@@ -10133,7 +11728,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>74</v>
@@ -10153,7 +11748,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>74</v>
@@ -10173,7 +11768,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>74</v>
@@ -10202,7 +11797,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>74</v>
@@ -10231,7 +11826,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>74</v>
@@ -10291,7 +11886,7 @@
         <v>0.0</v>
       </c>
       <c r="AM131" s="1" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="AN131" s="3">
         <v>2.0</v>
@@ -10323,7 +11918,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>80</v>
@@ -10343,7 +11938,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>80</v>
@@ -10363,7 +11958,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>80</v>
@@ -10395,7 +11990,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>80</v>
@@ -10455,7 +12050,7 @@
         <v>0.0</v>
       </c>
       <c r="AM135" s="1" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="AN135" s="3">
         <v>1.0</v>
@@ -10487,7 +12082,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>85</v>
@@ -10499,7 +12094,7 @@
         <v>51</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>55</v>
@@ -10507,7 +12102,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>85</v>
@@ -10527,7 +12122,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>85</v>
@@ -10550,7 +12145,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>85</v>
@@ -10559,7 +12154,7 @@
         <v>91</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>81</v>
@@ -10579,7 +12174,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>85</v>
@@ -10639,7 +12234,7 @@
         <v>1.0</v>
       </c>
       <c r="AM140" s="1" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="AN140" s="3">
         <v>1.0</v>
@@ -10671,7 +12266,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>95</v>
@@ -10691,7 +12286,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>95</v>
@@ -10700,13 +12295,13 @@
         <v>68</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>81</v>
       </c>
       <c r="L142" s="2" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="M142" s="3">
         <v>9.0</v>
@@ -10720,7 +12315,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>95</v>
@@ -10774,7 +12369,7 @@
         <v>3.0</v>
       </c>
       <c r="AM143" s="1" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="AN143" s="3">
         <v>1.0</v>
@@ -10806,7 +12401,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>99</v>
@@ -10826,7 +12421,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>99</v>
@@ -10858,7 +12453,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>99</v>
@@ -10887,7 +12482,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>99</v>
@@ -10941,7 +12536,7 @@
         <v>0.0</v>
       </c>
       <c r="AM147" s="1" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="AN147" s="3">
         <v>2.0</v>
@@ -11131,7 +12726,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>74</v>
@@ -11151,7 +12746,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>74</v>
@@ -11163,7 +12758,7 @@
         <v>82</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>107</v>
@@ -11171,7 +12766,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>74</v>
@@ -11191,7 +12786,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>74</v>
@@ -11220,7 +12815,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>74</v>
@@ -11280,7 +12875,7 @@
         <v>0.0</v>
       </c>
       <c r="AM6" s="1" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="AN6" s="3">
         <v>1.0</v>
@@ -11312,7 +12907,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>80</v>
@@ -11327,18 +12922,18 @@
         <v>81</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>55</v>
@@ -11352,7 +12947,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>80</v>
@@ -11372,13 +12967,13 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>53</v>
@@ -11392,7 +12987,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>80</v>
@@ -11404,7 +12999,7 @@
         <v>55</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>90</v>
@@ -11421,16 +13016,16 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>81</v>
@@ -11450,7 +13045,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>80</v>
@@ -11510,7 +13105,7 @@
         <v>1.0</v>
       </c>
       <c r="AM13" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="AN13" s="3">
         <v>2.0</v>
@@ -11542,7 +13137,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>85</v>
@@ -11557,18 +13152,18 @@
         <v>81</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -11582,7 +13177,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>85</v>
@@ -11597,7 +13192,7 @@
         <v>88</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>67</v>
@@ -11605,7 +13200,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>85</v>
@@ -11634,7 +13229,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>85</v>
@@ -11663,7 +13258,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>85</v>
@@ -11723,7 +13318,7 @@
         <v>0.0</v>
       </c>
       <c r="AM19" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="AN19" s="3">
         <v>2.0</v>
@@ -11755,7 +13350,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>95</v>
@@ -11767,7 +13362,7 @@
         <v>51</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>55</v>
@@ -11775,7 +13370,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>95</v>
@@ -11795,13 +13390,13 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>53</v>
@@ -11815,13 +13410,13 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>55</v>
@@ -11844,7 +13439,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>95</v>
@@ -11873,7 +13468,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>95</v>
@@ -11933,7 +13528,7 @@
         <v>0.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="AN25" s="3">
         <v>2.0</v>
@@ -11965,7 +13560,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>99</v>
@@ -11985,7 +13580,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>99</v>
@@ -12005,13 +13600,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>55</v>
@@ -12034,7 +13629,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>99</v>
@@ -12126,7 +13721,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>49</v>
@@ -12138,7 +13733,7 @@
         <v>122</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>51</v>
@@ -12146,7 +13741,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>49</v>
@@ -12166,13 +13761,13 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>96</v>
@@ -12181,24 +13776,24 @@
         <v>53</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>70</v>
@@ -12206,19 +13801,19 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>55</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>90</v>
@@ -12229,13 +13824,13 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>53</v>
@@ -12258,7 +13853,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>49</v>
@@ -12318,7 +13913,7 @@
         <v>0.0</v>
       </c>
       <c r="AM36" s="1" t="s">
-        <v>223</v>
+        <v>148</v>
       </c>
       <c r="AN36" s="3">
         <v>1.0</v>
@@ -12350,7 +13945,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>63</v>
@@ -12370,7 +13965,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>63</v>
@@ -12390,7 +13985,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>63</v>
@@ -12419,7 +14014,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>63</v>
@@ -12448,7 +14043,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>63</v>
@@ -12508,7 +14103,7 @@
         <v>1.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="AN41" s="3">
         <v>2.0</v>
@@ -12540,7 +14135,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>74</v>
@@ -12560,7 +14155,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>74</v>
@@ -12572,7 +14167,7 @@
         <v>87</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>87</v>
@@ -12580,7 +14175,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>74</v>
@@ -12609,19 +14204,19 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>74</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>100</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>70</v>
@@ -12632,7 +14227,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>74</v>
@@ -12692,7 +14287,7 @@
         <v>0.0</v>
       </c>
       <c r="AM46" s="1" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="AN46" s="3">
         <v>1.0</v>
@@ -12724,7 +14319,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>80</v>
@@ -12744,13 +14339,13 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>55</v>
@@ -12767,13 +14362,13 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>59</v>
@@ -12796,7 +14391,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>80</v>
@@ -12850,7 +14445,7 @@
         <v>0.0</v>
       </c>
       <c r="AM50" s="1" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="AN50" s="3">
         <v>1.0</v>
@@ -12882,7 +14477,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>85</v>
@@ -12902,27 +14497,27 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>56</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>85</v>
@@ -12942,13 +14537,13 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>55</v>
@@ -12965,13 +14560,13 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>53</v>
@@ -12994,7 +14589,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>85</v>
@@ -13057,7 +14652,7 @@
         <v>1.0</v>
       </c>
       <c r="AM56" s="1" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="AN56" s="3">
         <v>1.0</v>
@@ -13089,7 +14684,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>95</v>
@@ -13109,7 +14704,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>95</v>
@@ -13129,13 +14724,13 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>56</v>
@@ -13149,13 +14744,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>55</v>
@@ -13172,7 +14767,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>95</v>
@@ -13201,7 +14796,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>95</v>
@@ -13261,7 +14856,7 @@
         <v>0.0</v>
       </c>
       <c r="AM62" s="1" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="AN62" s="3">
         <v>1.0</v>
@@ -13293,7 +14888,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>99</v>
@@ -13305,7 +14900,7 @@
         <v>51</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>108</v>
@@ -13313,7 +14908,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>99</v>
@@ -13333,19 +14928,19 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>70</v>
@@ -13353,13 +14948,13 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>55</v>
@@ -13382,7 +14977,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>99</v>
@@ -13442,7 +15037,7 @@
         <v>0.0</v>
       </c>
       <c r="AM67" s="1" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="AN67" s="3">
         <v>1.0</v>
@@ -13474,7 +15069,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>49</v>
@@ -13486,7 +15081,7 @@
         <v>51</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>108</v>
@@ -13494,7 +15089,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>49</v>
@@ -13506,7 +15101,7 @@
         <v>53</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>65</v>
@@ -13514,13 +15109,13 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>53</v>
@@ -13529,24 +15124,24 @@
         <v>64</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>55</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>114</v>
@@ -13563,7 +15158,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>49</v>
@@ -13592,7 +15187,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>49</v>
@@ -13652,7 +15247,7 @@
         <v>0.0</v>
       </c>
       <c r="AM73" s="1" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="AN73" s="3">
         <v>2.0</v>
@@ -13684,7 +15279,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>63</v>
@@ -13704,13 +15299,13 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>55</v>
@@ -13724,7 +15319,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>63</v>
@@ -13736,7 +15331,7 @@
         <v>59</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>122</v>
@@ -13744,7 +15339,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>63</v>
@@ -13767,7 +15362,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>63</v>
@@ -13796,7 +15391,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>63</v>
@@ -13825,7 +15420,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>63</v>
@@ -13885,7 +15480,7 @@
         <v>0.0</v>
       </c>
       <c r="AM80" s="1" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="AN80" s="3">
         <v>2.0</v>
@@ -13917,7 +15512,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>74</v>
@@ -13937,7 +15532,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>74</v>
@@ -13966,7 +15561,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>74</v>
@@ -13995,7 +15590,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>74</v>
@@ -14052,7 +15647,7 @@
         <v>0.0</v>
       </c>
       <c r="AM84" s="1" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="AN84" s="3">
         <v>2.0</v>
@@ -14084,7 +15679,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>80</v>
@@ -14096,7 +15691,7 @@
         <v>51</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>114</v>
@@ -14104,13 +15699,13 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>55</v>
@@ -14124,7 +15719,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>80</v>
@@ -14144,19 +15739,19 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>70</v>
@@ -14164,13 +15759,13 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>55</v>
@@ -14187,19 +15782,19 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>114</v>
@@ -14210,7 +15805,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>80</v>
@@ -14270,7 +15865,7 @@
         <v>0.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="AN91" s="3">
         <v>0.0</v>
@@ -14302,7 +15897,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>85</v>
@@ -14322,13 +15917,13 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>55</v>
@@ -14342,7 +15937,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>85</v>
@@ -14362,19 +15957,19 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>114</v>
@@ -14382,7 +15977,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>85</v>
@@ -14411,13 +16006,13 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>53</v>
@@ -14440,7 +16035,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>85</v>
@@ -14500,7 +16095,7 @@
         <v>0.0</v>
       </c>
       <c r="AM98" s="1" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="AN98" s="3">
         <v>2.0</v>
@@ -14532,7 +16127,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>95</v>
@@ -14552,7 +16147,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>95</v>
@@ -14572,19 +16167,19 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>70</v>
@@ -14592,7 +16187,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>95</v>
@@ -14612,13 +16207,13 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>55</v>
@@ -14641,7 +16236,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>95</v>
@@ -14670,7 +16265,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>95</v>
@@ -14727,7 +16322,7 @@
         <v>1.0</v>
       </c>
       <c r="AM105" s="1" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="AN105" s="3">
         <v>2.0</v>
@@ -14759,7 +16354,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>99</v>
@@ -14779,13 +16374,13 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>55</v>
@@ -14799,13 +16394,13 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>55</v>
@@ -14828,7 +16423,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>99</v>
@@ -14885,7 +16480,7 @@
         <v>0.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="AN109" s="3">
         <v>1.0</v>
@@ -14917,7 +16512,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>49</v>
@@ -14937,13 +16532,13 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>55</v>
@@ -14957,7 +16552,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>49</v>
@@ -14977,13 +16572,13 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="I113" s="2" t="s">
         <v>55</v>
@@ -15006,7 +16601,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>49</v>
@@ -15035,7 +16630,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>49</v>
@@ -15092,7 +16687,7 @@
         <v>0.0</v>
       </c>
       <c r="AM115" s="1" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="AN115" s="3">
         <v>2.0</v>
@@ -15124,7 +16719,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>63</v>
@@ -15144,7 +16739,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>63</v>
@@ -15164,19 +16759,19 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>70</v>
@@ -15184,7 +16779,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>63</v>
@@ -15213,7 +16808,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>63</v>
@@ -15242,7 +16837,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>63</v>
@@ -15302,7 +16897,7 @@
         <v>0.0</v>
       </c>
       <c r="AM121" s="1" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="AN121" s="3">
         <v>2.0</v>
@@ -15334,7 +16929,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>74</v>
@@ -15354,7 +16949,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>74</v>
@@ -15377,13 +16972,13 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>74</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="I124" s="2" t="s">
         <v>53</v>
@@ -15406,7 +17001,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>74</v>
@@ -15466,7 +17061,7 @@
         <v>0.0</v>
       </c>
       <c r="AM125" s="1" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="AN125" s="3">
         <v>1.0</v>
@@ -15498,7 +17093,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>80</v>
@@ -15518,13 +17113,13 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>55</v>
@@ -15538,7 +17133,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>80</v>
@@ -15558,13 +17153,13 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I129" s="2" t="s">
         <v>55</v>
@@ -15587,7 +17182,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>80</v>
@@ -15599,13 +17194,13 @@
         <v>53</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="K130" s="2" t="s">
         <v>70</v>
       </c>
       <c r="L130" s="2" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="M130" s="3">
         <v>2.0</v>
@@ -15619,7 +17214,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>80</v>
@@ -15679,7 +17274,7 @@
         <v>0.0</v>
       </c>
       <c r="AM131" s="1" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="AN131" s="3">
         <v>2.0</v>
@@ -15711,7 +17306,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>85</v>
@@ -15723,7 +17318,7 @@
         <v>51</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>114</v>
@@ -15731,7 +17326,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>85</v>
@@ -15751,33 +17346,33 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I135" s="2" t="s">
         <v>55</v>
@@ -15800,7 +17395,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>85</v>
@@ -15812,7 +17407,7 @@
         <v>59</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="L136" s="2" t="s">
         <v>67</v>
@@ -15823,7 +17418,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>85</v>
@@ -15883,7 +17478,7 @@
         <v>0.0</v>
       </c>
       <c r="AM137" s="1" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="AN137" s="3">
         <v>1.0</v>
@@ -15915,7 +17510,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>95</v>
@@ -15935,13 +17530,13 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>55</v>
@@ -15955,7 +17550,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>95</v>
@@ -15975,13 +17570,13 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I141" s="2" t="s">
         <v>55</v>
@@ -16004,7 +17599,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>95</v>
@@ -16033,7 +17628,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>95</v>
@@ -16125,7 +17720,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>99</v>
@@ -16145,13 +17740,13 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>55</v>
@@ -16165,7 +17760,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>99</v>
@@ -16185,7 +17780,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>99</v>
@@ -16208,13 +17803,13 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I148" s="2" t="s">
         <v>53</v>
@@ -16237,7 +17832,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>99</v>
@@ -16297,7 +17892,7 @@
         <v>0.0</v>
       </c>
       <c r="AM149" s="1" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="AN149" s="3">
         <v>1.0</v>
@@ -16329,7 +17924,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>49</v>
@@ -16352,7 +17947,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>49</v>
@@ -16372,13 +17967,13 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>55</v>
@@ -16392,7 +17987,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>49</v>
@@ -16421,7 +18016,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>49</v>
@@ -16444,7 +18039,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>49</v>
@@ -16473,7 +18068,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>49</v>
@@ -16533,7 +18128,7 @@
         <v>1.0</v>
       </c>
       <c r="AM156" s="1" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="AN156" s="3">
         <v>2.0</v>
@@ -16565,7 +18160,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>63</v>
@@ -16577,7 +18172,7 @@
         <v>51</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>67</v>
@@ -16585,7 +18180,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>63</v>
@@ -16605,7 +18200,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>63</v>
@@ -16634,7 +18229,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>63</v>
@@ -16663,7 +18258,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>63</v>
@@ -16723,7 +18318,7 @@
         <v>0.0</v>
       </c>
       <c r="AM161" s="1" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="AN161" s="3">
         <v>2.0</v>
@@ -16755,7 +18350,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>74</v>
@@ -16775,7 +18370,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>74</v>
@@ -16795,7 +18390,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>74</v>
@@ -16824,7 +18419,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>74</v>
@@ -16853,7 +18448,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>74</v>
@@ -16907,7 +18502,7 @@
         <v>0.0</v>
       </c>
       <c r="AM166" s="1" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="AN166" s="3">
         <v>2.0</v>
@@ -16939,7 +18534,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>80</v>
@@ -16959,7 +18554,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>80</v>
@@ -16979,13 +18574,13 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I169" s="2" t="s">
         <v>55</v>
@@ -17002,7 +18597,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>80</v>
@@ -17014,7 +18609,7 @@
         <v>53</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="L170" s="2" t="s">
         <v>114</v>
@@ -17031,7 +18626,7 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>80</v>
@@ -17091,7 +18686,7 @@
         <v>0.0</v>
       </c>
       <c r="AM171" s="1" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="AN171" s="3">
         <v>1.0</v>
@@ -17123,7 +18718,7 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>85</v>
@@ -17138,18 +18733,18 @@
         <v>121</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I173" s="2" t="s">
         <v>55</v>
@@ -17172,7 +18767,7 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>85</v>
@@ -17201,7 +18796,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>85</v>
@@ -17258,7 +18853,7 @@
         <v>1.0</v>
       </c>
       <c r="AM175" s="1" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="AN175" s="3">
         <v>2.0</v>
@@ -17448,7 +19043,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>74</v>
@@ -17468,7 +19063,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>74</v>
@@ -17488,7 +19083,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>74</v>
@@ -17511,7 +19106,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>74</v>
@@ -17540,7 +19135,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>74</v>
@@ -17594,7 +19189,7 @@
         <v>0.0</v>
       </c>
       <c r="AM6" s="1" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="AN6" s="3">
         <v>1.0</v>
@@ -17626,7 +19221,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>80</v>
@@ -17646,7 +19241,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>80</v>
@@ -17666,13 +19261,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>53</v>
@@ -17689,7 +19284,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>80</v>
@@ -17749,7 +19344,7 @@
         <v>0.0</v>
       </c>
       <c r="AM10" s="1" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="AN10" s="3">
         <v>0.0</v>
@@ -17781,7 +19376,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>85</v>
@@ -17801,16 +19396,16 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="M12" s="3">
         <v>1.0</v>
@@ -17824,7 +19419,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>85</v>
@@ -17887,7 +19482,7 @@
         <v>1.0</v>
       </c>
       <c r="AM13" s="1" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="AN13" s="3">
         <v>1.0</v>
@@ -17919,7 +19514,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>95</v>
@@ -17939,22 +19534,22 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>55</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="M15" s="3">
         <v>1.0</v>
@@ -17968,13 +19563,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>53</v>
@@ -17997,7 +19592,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>95</v>
@@ -18051,7 +19646,7 @@
         <v>0.0</v>
       </c>
       <c r="AM17" s="1" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="AN17" s="3">
         <v>2.0</v>
@@ -18083,7 +19678,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>99</v>
@@ -18103,7 +19698,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>99</v>
@@ -18123,7 +19718,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>99</v>
@@ -18135,7 +19730,7 @@
         <v>53</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>70</v>
@@ -18143,13 +19738,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>53</v>
@@ -18172,7 +19767,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>99</v>
@@ -18226,7 +19821,7 @@
         <v>0.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="AN22" s="3">
         <v>1.0</v>
@@ -18258,7 +19853,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>49</v>
@@ -18278,7 +19873,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>49</v>
@@ -18298,7 +19893,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>49</v>
@@ -18318,13 +19913,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>69</v>
@@ -18347,7 +19942,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>49</v>
@@ -18401,7 +19996,7 @@
         <v>0.0</v>
       </c>
       <c r="AM27" s="1" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="AN27" s="3">
         <v>1.0</v>
@@ -18433,7 +20028,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>63</v>
@@ -18453,7 +20048,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>63</v>
@@ -18473,7 +20068,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>63</v>
@@ -18502,7 +20097,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>63</v>
@@ -18591,7 +20186,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>74</v>
@@ -18603,7 +20198,7 @@
         <v>51</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>55</v>
@@ -18611,7 +20206,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>74</v>
@@ -18620,7 +20215,7 @@
         <v>50</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>75</v>
@@ -18631,7 +20226,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>74</v>
@@ -18660,7 +20255,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>74</v>
@@ -18683,7 +20278,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>74</v>
@@ -18737,7 +20332,7 @@
         <v>1.0</v>
       </c>
       <c r="AM36" s="1" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="AN36" s="3">
         <v>1.0</v>
@@ -18769,7 +20364,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>80</v>
@@ -18789,7 +20384,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>80</v>
@@ -18809,7 +20404,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>80</v>
@@ -18818,7 +20413,7 @@
         <v>54</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>81</v>
@@ -18832,7 +20427,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>80</v>
@@ -18892,7 +20487,7 @@
         <v>2.0</v>
       </c>
       <c r="AM40" s="1" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="AN40" s="3">
         <v>0.0</v>
@@ -18924,7 +20519,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>85</v>
@@ -18944,7 +20539,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>85</v>
@@ -18964,13 +20559,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>53</v>
@@ -18993,7 +20588,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>85</v>
@@ -19047,7 +20642,7 @@
         <v>0.0</v>
       </c>
       <c r="AM44" s="1" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="AN44" s="3">
         <v>1.0</v>
@@ -19079,7 +20674,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>95</v>
@@ -19099,7 +20694,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>95</v>
@@ -19119,13 +20714,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>55</v>
@@ -19142,13 +20737,13 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>53</v>
@@ -19171,7 +20766,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>95</v>
@@ -19225,7 +20820,7 @@
         <v>1.0</v>
       </c>
       <c r="AM49" s="1" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="AN49" s="3">
         <v>1.0</v>
@@ -19257,7 +20852,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>99</v>
@@ -19277,7 +20872,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>99</v>
@@ -19297,19 +20892,19 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>81</v>
@@ -19317,13 +20912,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>53</v>
@@ -19346,7 +20941,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>99</v>
@@ -19400,7 +20995,7 @@
         <v>1.0</v>
       </c>
       <c r="AM54" s="1" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="AN54" s="3">
         <v>1.0</v>
@@ -19432,7 +21027,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>49</v>
@@ -19452,7 +21047,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>49</v>
@@ -19472,7 +21067,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>49</v>
@@ -19492,39 +21087,39 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>55</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>90</v>
@@ -19535,7 +21130,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>49</v>
@@ -19564,7 +21159,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>49</v>
@@ -19618,7 +21213,7 @@
         <v>0.0</v>
       </c>
       <c r="AM61" s="1" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="AN61" s="3">
         <v>1.0</v>
@@ -19650,7 +21245,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>63</v>
@@ -19670,7 +21265,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>63</v>
@@ -19690,7 +21285,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>63</v>
@@ -19710,7 +21305,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>63</v>
@@ -19739,7 +21334,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>63</v>
@@ -19796,7 +21391,7 @@
         <v>3.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="AN66" s="3">
         <v>1.0</v>
@@ -19828,7 +21423,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>74</v>
@@ -19848,13 +21443,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>55</v>
@@ -19868,7 +21463,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>74</v>
@@ -19888,7 +21483,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>74</v>
@@ -19917,7 +21512,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>74</v>
@@ -19946,7 +21541,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>74</v>
@@ -20006,7 +21601,7 @@
         <v>1.0</v>
       </c>
       <c r="AM72" s="1" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="AN72" s="3">
         <v>2.0</v>
@@ -20038,7 +21633,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>80</v>
@@ -20058,7 +21653,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>80</v>
@@ -20078,13 +21673,13 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>96</v>
@@ -20098,13 +21693,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>53</v>
@@ -20127,7 +21722,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>80</v>
@@ -20181,7 +21776,7 @@
         <v>0.0</v>
       </c>
       <c r="AM77" s="1" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="AN77" s="3">
         <v>1.0</v>
@@ -20213,7 +21808,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>85</v>
@@ -20233,13 +21828,13 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>96</v>
@@ -20253,7 +21848,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>85</v>
@@ -20273,7 +21868,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>85</v>
@@ -20282,7 +21877,7 @@
         <v>54</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>81</v>
@@ -20296,7 +21891,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>85</v>
@@ -20356,7 +21951,7 @@
         <v>1.0</v>
       </c>
       <c r="AM82" s="1" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="AN82" s="3">
         <v>0.0</v>
@@ -20388,7 +21983,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>95</v>
@@ -20408,7 +22003,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>95</v>
@@ -20428,27 +22023,27 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>95</v>
@@ -20468,13 +22063,13 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>53</v>
@@ -20497,7 +22092,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>95</v>
@@ -20551,7 +22146,7 @@
         <v>1.0</v>
       </c>
       <c r="AM88" s="1" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="AN88" s="3">
         <v>1.0</v>
@@ -20583,7 +22178,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>99</v>
@@ -20603,7 +22198,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>99</v>
@@ -20657,7 +22252,7 @@
         <v>2.0</v>
       </c>
       <c r="AM90" s="1" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="AN90" s="3">
         <v>0.0</v>
@@ -20689,7 +22284,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>49</v>
@@ -20709,13 +22304,13 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>65</v>
@@ -20729,7 +22324,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>49</v>
@@ -20749,7 +22344,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>49</v>
@@ -20778,7 +22373,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>49</v>
@@ -20807,7 +22402,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>49</v>
@@ -20861,7 +22456,7 @@
         <v>1.0</v>
       </c>
       <c r="AM96" s="1" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="AN96" s="3">
         <v>2.0</v>
@@ -20893,7 +22488,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>63</v>
@@ -20913,7 +22508,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>63</v>
@@ -20933,7 +22528,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>63</v>
@@ -20945,7 +22540,7 @@
         <v>55</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>108</v>
@@ -20962,7 +22557,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>63</v>
@@ -20991,7 +22586,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>63</v>
@@ -21051,7 +22646,7 @@
         <v>1.0</v>
       </c>
       <c r="AM101" s="1" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="AN101" s="3">
         <v>2.0</v>
@@ -21083,7 +22678,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>74</v>
@@ -21103,13 +22698,13 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>55</v>
@@ -21123,7 +22718,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>74</v>
@@ -21152,7 +22747,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>74</v>
@@ -21175,7 +22770,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>74</v>
@@ -21229,7 +22824,7 @@
         <v>0.0</v>
       </c>
       <c r="AM106" s="1" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="AN106" s="3">
         <v>1.0</v>
@@ -21261,7 +22856,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>80</v>
@@ -21281,13 +22876,13 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>53</v>
@@ -21310,7 +22905,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>80</v>
@@ -21364,7 +22959,7 @@
         <v>0.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="AN109" s="3">
         <v>1.0</v>
@@ -21396,7 +22991,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>85</v>
@@ -21416,7 +23011,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>85</v>
@@ -21436,7 +23031,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>85</v>
@@ -21456,13 +23051,13 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>55</v>
@@ -21476,13 +23071,13 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I114" s="2" t="s">
         <v>53</v>
@@ -21505,7 +23100,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>85</v>
@@ -21568,7 +23163,7 @@
         <v>1.0</v>
       </c>
       <c r="AM115" s="1" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="AN115" s="3">
         <v>1.0</v>
@@ -21600,13 +23195,13 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>55</v>
@@ -21620,7 +23215,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>95</v>
@@ -21640,7 +23235,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>95</v>
@@ -21660,7 +23255,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>95</v>
@@ -21672,21 +23267,21 @@
         <v>56</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="I120" s="2" t="s">
         <v>55</v>
@@ -21709,13 +23304,13 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>53</v>
@@ -21738,7 +23333,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>95</v>
@@ -21792,7 +23387,7 @@
         <v>0.0</v>
       </c>
       <c r="AM122" s="1" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="AN122" s="3">
         <v>2.0</v>
@@ -21824,7 +23419,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>99</v>
@@ -21844,13 +23439,13 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>55</v>
@@ -21864,7 +23459,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>99</v>
@@ -21884,7 +23479,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>99</v>
@@ -21913,7 +23508,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>99</v>
@@ -21967,7 +23562,7 @@
         <v>1.0</v>
       </c>
       <c r="AM127" s="1" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="AN127" s="3">
         <v>1.0</v>
@@ -21999,7 +23594,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>49</v>
@@ -22019,7 +23614,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>49</v>
@@ -22039,13 +23634,13 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="I130" s="2" t="s">
         <v>55</v>
@@ -22062,7 +23657,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>49</v>
@@ -22122,7 +23717,7 @@
         <v>0.0</v>
       </c>
       <c r="AM131" s="1" t="s">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="AN131" s="3">
         <v>0.0</v>
@@ -22154,7 +23749,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>63</v>
@@ -22174,13 +23769,13 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>96</v>
@@ -22189,12 +23784,12 @@
         <v>53</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>63</v>
@@ -22214,7 +23809,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>63</v>
@@ -22234,7 +23829,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>63</v>
@@ -22263,13 +23858,13 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="I137" s="2" t="s">
         <v>69</v>
@@ -22292,7 +23887,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>63</v>
@@ -22352,7 +23947,7 @@
         <v>0.0</v>
       </c>
       <c r="AM138" s="1" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="AN138" s="3">
         <v>2.0</v>
@@ -22542,7 +24137,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>99</v>
@@ -22562,7 +24157,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>99</v>
@@ -22582,7 +24177,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>99</v>
@@ -22605,7 +24200,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>99</v>
@@ -22634,7 +24229,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>99</v>
@@ -22643,7 +24238,7 @@
         <v>92</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>81</v>
@@ -22663,7 +24258,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>99</v>
@@ -22717,7 +24312,7 @@
         <v>0.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="AN7" s="3">
         <v>2.0</v>
@@ -22749,7 +24344,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>49</v>
@@ -22769,7 +24364,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>49</v>
@@ -22789,7 +24384,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>49</v>
@@ -22818,7 +24413,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -22847,7 +24442,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>49</v>
@@ -22901,7 +24496,7 @@
         <v>0.0</v>
       </c>
       <c r="AM12" s="1" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="AN12" s="3">
         <v>2.0</v>
@@ -22933,7 +24528,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>63</v>
@@ -22953,7 +24548,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>63</v>
@@ -22973,13 +24568,13 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>55</v>
@@ -23005,7 +24600,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>63</v>
@@ -23059,7 +24654,7 @@
         <v>1.0</v>
       </c>
       <c r="AM16" s="1" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="AN16" s="3">
         <v>1.0</v>
@@ -23091,7 +24686,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>74</v>
@@ -23111,7 +24706,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>74</v>
@@ -23131,7 +24726,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>74</v>
@@ -23147,7 +24742,7 @@
         <v>55</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>121</v>
@@ -23158,7 +24753,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>74</v>
@@ -23191,7 +24786,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>74</v>
@@ -23252,7 +24847,7 @@
         <v>0.0</v>
       </c>
       <c r="AM21" s="1" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="AN21" s="3">
         <v>1.0</v>
@@ -23284,7 +24879,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>80</v>
@@ -23304,7 +24899,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>80</v>
@@ -23324,13 +24919,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>55</v>
@@ -23353,7 +24948,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>80</v>
@@ -23413,7 +25008,7 @@
         <v>0.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="AN25" s="3">
         <v>1.0</v>
@@ -23445,7 +25040,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>85</v>
@@ -23465,7 +25060,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>85</v>
@@ -23485,13 +25080,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>53</v>
@@ -23514,7 +25109,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>85</v>
@@ -23537,7 +25132,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>85</v>
@@ -23597,7 +25192,7 @@
         <v>0.0</v>
       </c>
       <c r="AM30" s="1" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="AN30" s="3">
         <v>1.0</v>
@@ -23629,7 +25224,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>95</v>
@@ -23649,7 +25244,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>95</v>
@@ -23669,7 +25264,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>95</v>
@@ -23679,7 +25274,7 @@
       <c r="E33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>55</v>
@@ -23696,7 +25291,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>95</v>
@@ -23706,7 +25301,7 @@
       <c r="E34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>53</v>
@@ -23723,7 +25318,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>95</v>
@@ -23736,7 +25331,7 @@
         <v>0.0</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>106</v>
@@ -23787,7 +25382,7 @@
         <v>0.0</v>
       </c>
       <c r="AM35" s="1" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="AN35" s="3">
         <v>0.0</v>
@@ -23819,7 +25414,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>99</v>
@@ -23839,7 +25434,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>99</v>
@@ -23859,13 +25454,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>59</v>
@@ -23888,7 +25483,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>99</v>
@@ -23948,7 +25543,7 @@
         <v>0.0</v>
       </c>
       <c r="AM39" s="1" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="AN39" s="3">
         <v>1.0</v>
@@ -23980,7 +25575,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>49</v>
@@ -24000,13 +25595,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>55</v>
@@ -24023,13 +25618,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>53</v>
@@ -24052,7 +25647,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>49</v>
@@ -24106,7 +25701,7 @@
         <v>3.0</v>
       </c>
       <c r="AM43" s="1" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="AN43" s="3">
         <v>1.0</v>
@@ -24138,7 +25733,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>63</v>
@@ -24158,7 +25753,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>63</v>
@@ -24178,13 +25773,13 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>55</v>
@@ -24207,13 +25802,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>53</v>
@@ -24236,7 +25831,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>63</v>
@@ -24322,7 +25917,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>74</v>
@@ -24342,7 +25937,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>74</v>
@@ -24374,7 +25969,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>74</v>
@@ -24437,7 +26032,7 @@
         <v>0.0</v>
       </c>
       <c r="AM51" s="1" t="s">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="AN51" s="3">
         <v>1.0</v>
@@ -24469,7 +26064,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>80</v>
@@ -24489,7 +26084,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>80</v>
@@ -24509,13 +26104,13 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>53</v>
@@ -24538,7 +26133,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>80</v>
@@ -24592,7 +26187,7 @@
         <v>2.0</v>
       </c>
       <c r="AM55" s="1" t="s">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="AN55" s="3">
         <v>1.0</v>
@@ -24624,7 +26219,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>85</v>
@@ -24644,7 +26239,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>85</v>
@@ -24664,13 +26259,13 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>53</v>
@@ -24693,7 +26288,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>85</v>
@@ -24747,7 +26342,7 @@
         <v>0.0</v>
       </c>
       <c r="AM59" s="1" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="AN59" s="3">
         <v>1.0</v>
@@ -24779,7 +26374,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>95</v>
@@ -24799,7 +26394,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>95</v>
@@ -24819,7 +26414,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>95</v>
@@ -24873,7 +26468,7 @@
         <v>0.0</v>
       </c>
       <c r="AM62" s="1" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="AN62" s="3">
         <v>0.0</v>
@@ -24905,7 +26500,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>99</v>
@@ -24925,7 +26520,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>99</v>
@@ -24945,16 +26540,16 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>81</v>
@@ -24977,7 +26572,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>99</v>
@@ -25031,7 +26626,7 @@
         <v>0.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="AN66" s="3">
         <v>1.0</v>
@@ -25063,7 +26658,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>49</v>
@@ -25083,7 +26678,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>49</v>
@@ -25103,13 +26698,13 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>53</v>
@@ -25132,7 +26727,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>49</v>
@@ -25186,7 +26781,7 @@
         <v>0.0</v>
       </c>
       <c r="AM70" s="1" t="s">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="AN70" s="3">
         <v>1.0</v>
@@ -25218,7 +26813,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>63</v>
@@ -25238,7 +26833,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>63</v>
@@ -25258,7 +26853,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>63</v>
@@ -25287,7 +26882,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>63</v>
@@ -25341,7 +26936,7 @@
         <v>0.0</v>
       </c>
       <c r="AM74" s="1" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="AN74" s="3">
         <v>1.0</v>
@@ -25373,7 +26968,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>74</v>
@@ -25393,7 +26988,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>74</v>
@@ -25413,13 +27008,13 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>74</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>55</v>
@@ -25442,7 +27037,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>74</v>
@@ -25465,7 +27060,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>74</v>
@@ -25519,7 +27114,7 @@
         <v>1.0</v>
       </c>
       <c r="AM79" s="1" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="AN79" s="3">
         <v>1.0</v>
@@ -25551,7 +27146,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>80</v>
@@ -25571,13 +27166,13 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>56</v>
@@ -25600,7 +27195,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>80</v>
@@ -25660,7 +27255,7 @@
         <v>0.0</v>
       </c>
       <c r="AM82" s="1" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="AN82" s="3">
         <v>1.0</v>
@@ -25692,7 +27287,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>85</v>
@@ -25712,7 +27307,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>85</v>
@@ -25732,7 +27327,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>85</v>
@@ -25761,13 +27356,13 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>56</v>
@@ -25790,7 +27385,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>85</v>
@@ -25850,7 +27445,7 @@
         <v>0.0</v>
       </c>
       <c r="AM87" s="1" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="AN87" s="3">
         <v>2.0</v>
@@ -25882,7 +27477,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>95</v>
@@ -25902,7 +27497,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>95</v>
@@ -25922,7 +27517,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>95</v>
@@ -25951,7 +27546,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>95</v>
@@ -26005,7 +27600,7 @@
         <v>1.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="AN91" s="3">
         <v>1.0</v>
@@ -26037,7 +27632,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>99</v>
@@ -26057,7 +27652,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>99</v>
@@ -26077,7 +27672,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>99</v>
@@ -26106,7 +27701,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>99</v>
@@ -26160,7 +27755,7 @@
         <v>0.0</v>
       </c>
       <c r="AM95" s="1" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="AN95" s="3">
         <v>1.0</v>
@@ -26192,7 +27787,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>49</v>
@@ -26212,7 +27807,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>49</v>
@@ -26232,13 +27827,13 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>55</v>
@@ -26261,7 +27856,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>49</v>
@@ -26290,7 +27885,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>49</v>
@@ -26344,7 +27939,7 @@
         <v>0.0</v>
       </c>
       <c r="AM100" s="1" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="AN100" s="3">
         <v>2.0</v>
@@ -26376,7 +27971,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>63</v>
@@ -26396,7 +27991,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>63</v>
@@ -26416,7 +28011,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>63</v>
@@ -26445,7 +28040,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>63</v>
@@ -26499,7 +28094,7 @@
         <v>2.0</v>
       </c>
       <c r="AM104" s="1" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="AN104" s="3">
         <v>1.0</v>
@@ -26531,7 +28126,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>74</v>
@@ -26551,7 +28146,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>74</v>
@@ -26571,7 +28166,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>74</v>
@@ -26583,7 +28178,7 @@
         <v>96</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="L107" s="2" t="s">
         <v>52</v>
@@ -26600,7 +28195,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>74</v>
@@ -26629,7 +28224,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>74</v>
@@ -26689,7 +28284,7 @@
         <v>2.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="AN109" s="3">
         <v>2.0</v>
@@ -26721,7 +28316,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>80</v>
@@ -26741,7 +28336,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>80</v>
@@ -26761,7 +28356,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>80</v>
@@ -26784,7 +28379,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>80</v>
@@ -26813,7 +28408,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>80</v>
@@ -26867,7 +28462,7 @@
         <v>0.0</v>
       </c>
       <c r="AM114" s="1" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="AN114" s="3">
         <v>1.0</v>
@@ -26899,7 +28494,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>85</v>
@@ -26919,7 +28514,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>85</v>
@@ -26939,7 +28534,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>85</v>
@@ -26959,7 +28554,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>85</v>
@@ -26988,7 +28583,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>85</v>
@@ -27045,7 +28640,7 @@
         <v>0.0</v>
       </c>
       <c r="AM119" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="AN119" s="3">
         <v>1.0</v>
@@ -27077,7 +28672,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>95</v>
@@ -27097,7 +28692,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>95</v>
@@ -27117,7 +28712,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>95</v>
@@ -27146,7 +28741,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>95</v>
@@ -27169,7 +28764,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>95</v>
@@ -27226,7 +28821,7 @@
         <v>1.0</v>
       </c>
       <c r="AM124" s="1" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="AN124" s="3">
         <v>1.0</v>
@@ -27258,7 +28853,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>99</v>
@@ -27278,7 +28873,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>99</v>
@@ -27298,7 +28893,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>99</v>
@@ -27318,7 +28913,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>99</v>
@@ -27347,7 +28942,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>99</v>
@@ -27407,7 +29002,7 @@
         <v>1.0</v>
       </c>
       <c r="AM129" s="1" t="s">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="AN129" s="3">
         <v>1.0</v>
@@ -27439,7 +29034,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>49</v>
@@ -27459,7 +29054,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>49</v>
@@ -27479,7 +29074,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>49</v>
@@ -27499,13 +29094,13 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="I133" s="2" t="s">
         <v>55</v>
@@ -27528,13 +29123,13 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I134" s="2" t="s">
         <v>53</v>
@@ -27557,7 +29152,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>49</v>
@@ -27611,7 +29206,7 @@
         <v>0.0</v>
       </c>
       <c r="AM135" s="1" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="AN135" s="3">
         <v>2.0</v>
@@ -27643,7 +29238,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>63</v>
@@ -27663,7 +29258,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>63</v>
@@ -27683,7 +29278,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>63</v>
@@ -27703,7 +29298,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>63</v>
@@ -27732,13 +29327,13 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I140" s="2" t="s">
         <v>53</v>
@@ -27761,7 +29356,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>63</v>
@@ -27815,7 +29410,7 @@
         <v>0.0</v>
       </c>
       <c r="AM141" s="1" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="AN141" s="3">
         <v>2.0</v>
